--- a/research/traditional_assets/database/data/ghana/ghana_food_processing.xlsx
+++ b/research/traditional_assets/database/data/ghana/ghana_food_processing.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,115 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.04</v>
-      </c>
-      <c r="F2">
-        <v>1.548</v>
+        <v>0.1338</v>
       </c>
       <c r="G2">
-        <v>0.07523302263648469</v>
+        <v>-0.01319742489270386</v>
       </c>
       <c r="H2">
-        <v>0.07523302263648469</v>
+        <v>-0.01319742489270386</v>
       </c>
       <c r="I2">
-        <v>-0.0237017310252996</v>
+        <v>-0.1068669527896996</v>
       </c>
       <c r="J2">
-        <v>-0.0237017310252996</v>
+        <v>-0.1068669527896996</v>
       </c>
       <c r="K2">
-        <v>-1.79</v>
+        <v>-15.53</v>
       </c>
       <c r="L2">
-        <v>-0.02383488681757657</v>
+        <v>-0.1666309012875536</v>
       </c>
       <c r="M2">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>1.314060446780552e-05</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.0005586592178770949</v>
+        <v>-0</v>
       </c>
       <c r="P2">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>1.314060446780552e-05</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-0.0005586592178770949</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>5.52</v>
+        <v>2.843</v>
       </c>
       <c r="V2">
-        <v>0.07253613666228646</v>
+        <v>0.07123527937860184</v>
       </c>
       <c r="W2">
-        <v>-0.03995535714285715</v>
+        <v>0.1154324543840429</v>
       </c>
       <c r="X2">
-        <v>0.09529227346391106</v>
+        <v>1.502450250040767</v>
       </c>
       <c r="Y2">
-        <v>-0.1352476306067682</v>
+        <v>-1.387017795656724</v>
       </c>
       <c r="Z2">
-        <v>1.996809359212975</v>
+        <v>1.590905211409453</v>
       </c>
       <c r="AA2">
-        <v>-0.04732783834086679</v>
+        <v>-0.2037577040644605</v>
       </c>
       <c r="AB2">
-        <v>0.09529227346391106</v>
+        <v>0.2617798904501262</v>
       </c>
       <c r="AC2">
-        <v>-0.1426201118047778</v>
+        <v>-0.4655375945145868</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>85.55</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>85.55</v>
       </c>
       <c r="AG2">
-        <v>-5.52</v>
+        <v>82.70699999999999</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.6818906424358361</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>2.005861664712779</v>
       </c>
       <c r="AJ2">
-        <v>-0.07820912439784641</v>
+        <v>0.6745149530652357</v>
       </c>
       <c r="AK2">
-        <v>-0.1547085201793721</v>
+        <v>2.077699902027282</v>
       </c>
       <c r="AL2">
-        <v>0.289</v>
+        <v>7.45</v>
       </c>
       <c r="AM2">
-        <v>-0.13</v>
+        <v>6.433</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>-61.9927536231884</v>
       </c>
       <c r="AO2">
-        <v>-6.159169550173011</v>
+        <v>-1.336912751677853</v>
       </c>
       <c r="AP2">
-        <v>-1.652694610778443</v>
+        <v>-59.93260869565216</v>
       </c>
       <c r="AQ2">
-        <v>13.69230769230769</v>
+        <v>-1.548266749572517</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +716,243 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.04</v>
-      </c>
-      <c r="F3">
-        <v>1.548</v>
+        <v>0.0266</v>
       </c>
       <c r="G3">
-        <v>0.07523302263648469</v>
+        <v>0.02756539235412475</v>
       </c>
       <c r="H3">
-        <v>0.07523302263648469</v>
+        <v>0.02756539235412475</v>
       </c>
       <c r="I3">
-        <v>-0.0237017310252996</v>
+        <v>-0.0352112676056338</v>
       </c>
       <c r="J3">
-        <v>-0.0237017310252996</v>
+        <v>-0.0352112676056338</v>
       </c>
       <c r="K3">
-        <v>-1.79</v>
+        <v>-1.63</v>
       </c>
       <c r="L3">
-        <v>-0.02383488681757657</v>
+        <v>-0.03279678068410462</v>
       </c>
       <c r="M3">
-        <v>0.001</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>1.314060446780552e-05</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.0005586592178770949</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>0.001</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>1.314060446780552e-05</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0.0005586592178770949</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>5.52</v>
+        <v>2.19</v>
       </c>
       <c r="V3">
-        <v>0.07253613666228646</v>
+        <v>0.06151685393258426</v>
       </c>
       <c r="W3">
-        <v>-0.03995535714285715</v>
+        <v>-0.0395631067961165</v>
       </c>
       <c r="X3">
-        <v>0.09529227346391106</v>
+        <v>0.2502843511710505</v>
       </c>
       <c r="Y3">
-        <v>-0.1352476306067682</v>
+        <v>-0.289847457967167</v>
       </c>
       <c r="Z3">
-        <v>1.996809359212975</v>
+        <v>1.392937219730942</v>
       </c>
       <c r="AA3">
-        <v>-0.04732783834086679</v>
+        <v>-0.04904708520179371</v>
       </c>
       <c r="AB3">
-        <v>0.09529227346391106</v>
+        <v>0.2343229828609253</v>
       </c>
       <c r="AC3">
-        <v>-0.1426201118047778</v>
+        <v>-0.283370068062719</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AG3">
-        <v>-5.52</v>
+        <v>4.66</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.1613663133097762</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.2333901192504259</v>
       </c>
       <c r="AJ3">
-        <v>-0.07820912439784641</v>
+        <v>0.1157476403378043</v>
       </c>
       <c r="AK3">
-        <v>-0.1547085201793721</v>
+        <v>0.1715758468335788</v>
       </c>
       <c r="AL3">
-        <v>0.289</v>
+        <v>1.59</v>
       </c>
       <c r="AM3">
-        <v>-0.13</v>
+        <v>0.7020000000000001</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>5.614754098360655</v>
       </c>
       <c r="AO3">
-        <v>-6.159169550173011</v>
+        <v>-1.10062893081761</v>
       </c>
       <c r="AP3">
-        <v>-1.652694610778443</v>
+        <v>3.819672131147541</v>
       </c>
       <c r="AQ3">
-        <v>13.69230769230769</v>
+        <v>-2.492877492877493</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cocoa Processing Company Limited (GHSE:CPC)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Food Processing</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.241</v>
+      </c>
+      <c r="G4">
+        <v>-0.05977011494252873</v>
+      </c>
+      <c r="H4">
+        <v>-0.05977011494252873</v>
+      </c>
+      <c r="I4">
+        <v>-0.1887356321839081</v>
+      </c>
+      <c r="J4">
+        <v>-0.1887356321839081</v>
+      </c>
+      <c r="K4">
+        <v>-13.9</v>
+      </c>
+      <c r="L4">
+        <v>-0.3195402298850575</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0.653</v>
+      </c>
+      <c r="V4">
+        <v>0.151508120649652</v>
+      </c>
+      <c r="W4">
+        <v>0.2704280155642024</v>
+      </c>
+      <c r="X4">
+        <v>2.754616148910484</v>
+      </c>
+      <c r="Y4">
+        <v>-2.484188133346282</v>
+      </c>
+      <c r="Z4">
+        <v>1.899314500283805</v>
+      </c>
+      <c r="AA4">
+        <v>-0.3584683229271274</v>
+      </c>
+      <c r="AB4">
+        <v>0.2892367980393271</v>
+      </c>
+      <c r="AC4">
+        <v>-0.6477051209664545</v>
+      </c>
+      <c r="AD4">
+        <v>78.7</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>78.7</v>
+      </c>
+      <c r="AG4">
+        <v>78.047</v>
+      </c>
+      <c r="AH4">
+        <v>0.9480785447536442</v>
+      </c>
+      <c r="AI4">
+        <v>5.917293233082709</v>
+      </c>
+      <c r="AJ4">
+        <v>0.9476668649902255</v>
+      </c>
+      <c r="AK4">
+        <v>6.171186842729505</v>
+      </c>
+      <c r="AL4">
+        <v>5.86</v>
+      </c>
+      <c r="AM4">
+        <v>5.731</v>
+      </c>
+      <c r="AN4">
+        <v>-30.26923076923077</v>
+      </c>
+      <c r="AO4">
+        <v>-1.401023890784983</v>
+      </c>
+      <c r="AP4">
+        <v>-30.01807692307692</v>
+      </c>
+      <c r="AQ4">
+        <v>-1.43255976269412</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/ghana/ghana_food_processing.xlsx
+++ b/research/traditional_assets/database/data/ghana/ghana_food_processing.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,115 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1338</v>
+        <v>0.07429999999999999</v>
       </c>
       <c r="G2">
-        <v>-0.01319742489270386</v>
+        <v>-0.06349458748700385</v>
       </c>
       <c r="H2">
-        <v>-0.01319742489270386</v>
+        <v>-0.06356797749373126</v>
       </c>
       <c r="I2">
-        <v>-0.1068669527896996</v>
+        <v>-0.1276252216989786</v>
       </c>
       <c r="J2">
-        <v>-0.1068669527896996</v>
+        <v>-0.1063543514158155</v>
       </c>
       <c r="K2">
-        <v>-15.53</v>
+        <v>-12.199</v>
       </c>
       <c r="L2">
-        <v>-0.1666309012875536</v>
+        <v>-0.1492141153446272</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.0001118912417130549</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.0003278957291581277</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.0001118912417130549</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>-0.0003278957291581277</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>2.843</v>
+        <v>4.583</v>
       </c>
       <c r="V2">
-        <v>0.07123527937860184</v>
+        <v>0.1281993901927327</v>
       </c>
       <c r="W2">
-        <v>0.1154324543840429</v>
+        <v>-0.02404809619238477</v>
       </c>
       <c r="X2">
-        <v>1.502450250040767</v>
+        <v>0.1706441163415156</v>
       </c>
       <c r="Y2">
-        <v>-1.387017795656724</v>
+        <v>-0.1946922125339004</v>
       </c>
       <c r="Z2">
-        <v>1.590905211409453</v>
+        <v>1.860055058812823</v>
       </c>
       <c r="AA2">
-        <v>-0.2037577040644605</v>
+        <v>-0.08606557377049182</v>
       </c>
       <c r="AB2">
-        <v>0.2617798904501262</v>
+        <v>0.1642350190330101</v>
       </c>
       <c r="AC2">
-        <v>-0.4655375945145868</v>
+        <v>-0.2434421796318185</v>
       </c>
       <c r="AD2">
-        <v>85.55</v>
+        <v>57.753</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>85.55</v>
+        <v>57.753</v>
       </c>
       <c r="AG2">
-        <v>82.70699999999999</v>
+        <v>53.17</v>
       </c>
       <c r="AH2">
-        <v>0.6818906424358361</v>
+        <v>0.6176659322795235</v>
       </c>
       <c r="AI2">
-        <v>2.005861664712779</v>
+        <v>0.6566721244371674</v>
       </c>
       <c r="AJ2">
-        <v>0.6745149530652357</v>
+        <v>0.5979599410699626</v>
       </c>
       <c r="AK2">
-        <v>2.077699902027282</v>
+        <v>0.6377976368979787</v>
       </c>
       <c r="AL2">
-        <v>7.45</v>
+        <v>6.17</v>
       </c>
       <c r="AM2">
-        <v>6.433</v>
+        <v>0.6699999999999999</v>
       </c>
       <c r="AN2">
-        <v>-61.9927536231884</v>
+        <v>-21.00873044743543</v>
       </c>
       <c r="AO2">
-        <v>-1.336912751677853</v>
+        <v>-1.691085899513776</v>
       </c>
       <c r="AP2">
-        <v>-59.93260869565216</v>
+        <v>-19.34157875591124</v>
       </c>
       <c r="AQ2">
-        <v>-1.548266749572517</v>
+        <v>-15.57313432835821</v>
       </c>
     </row>
     <row r="3">
@@ -716,115 +719,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0266</v>
+        <v>0.07429999999999999</v>
       </c>
       <c r="G3">
-        <v>0.02756539235412475</v>
+        <v>-0.005061224489795919</v>
       </c>
       <c r="H3">
-        <v>0.02756539235412475</v>
+        <v>-0.005061224489795919</v>
       </c>
       <c r="I3">
-        <v>-0.0352112676056338</v>
+        <v>-0.003918367346938775</v>
       </c>
       <c r="J3">
-        <v>-0.0352112676056338</v>
+        <v>-0.001959183673469388</v>
       </c>
       <c r="K3">
-        <v>-1.63</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="L3">
-        <v>-0.03279678068410462</v>
+        <v>-0.01402040816326531</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.004</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0001273885350318471</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.005822416302765647</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.004</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.0001273885350318471</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0.005822416302765647</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>2.19</v>
+        <v>2.58</v>
       </c>
       <c r="V3">
-        <v>0.06151685393258426</v>
+        <v>0.08216560509554141</v>
       </c>
       <c r="W3">
-        <v>-0.0395631067961165</v>
+        <v>-0.03053333333333334</v>
       </c>
       <c r="X3">
-        <v>0.2502843511710505</v>
+        <v>0.1706441163415156</v>
       </c>
       <c r="Y3">
-        <v>-0.289847457967167</v>
+        <v>-0.2011774496748489</v>
       </c>
       <c r="Z3">
-        <v>1.392937219730942</v>
+        <v>1.804123711340206</v>
       </c>
       <c r="AA3">
-        <v>-0.04904708520179371</v>
+        <v>-0.003534609720176731</v>
       </c>
       <c r="AB3">
-        <v>0.2343229828609253</v>
+        <v>0.1642350190330101</v>
       </c>
       <c r="AC3">
-        <v>-0.283370068062719</v>
+        <v>-0.1677696287531868</v>
       </c>
       <c r="AD3">
-        <v>6.85</v>
+        <v>4.75</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6.85</v>
+        <v>4.75</v>
       </c>
       <c r="AG3">
-        <v>4.66</v>
+        <v>2.17</v>
       </c>
       <c r="AH3">
-        <v>0.1613663133097762</v>
+        <v>0.1313969571230982</v>
       </c>
       <c r="AI3">
-        <v>0.2333901192504259</v>
+        <v>0.1983298538622129</v>
       </c>
       <c r="AJ3">
-        <v>0.1157476403378043</v>
+        <v>0.06464104855525767</v>
       </c>
       <c r="AK3">
-        <v>0.1715758468335788</v>
+        <v>0.1015442208703791</v>
       </c>
       <c r="AL3">
-        <v>1.59</v>
+        <v>2.44</v>
       </c>
       <c r="AM3">
-        <v>0.7020000000000001</v>
+        <v>-0.6600000000000001</v>
       </c>
       <c r="AN3">
-        <v>5.614754098360655</v>
+        <v>2.159090909090909</v>
       </c>
       <c r="AO3">
-        <v>-1.10062893081761</v>
+        <v>-0.07868852459016394</v>
       </c>
       <c r="AP3">
-        <v>3.819672131147541</v>
+        <v>0.9863636363636362</v>
       </c>
       <c r="AQ3">
-        <v>-2.492877492877493</v>
+        <v>0.2909090909090908</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cocoa Processing Company Limited (GHSE:CPC)</t>
+          <t>Hords Plc (GHSE:HORDS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,25 +850,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.241</v>
+        <v>0.114</v>
       </c>
       <c r="G4">
-        <v>-0.05977011494252873</v>
+        <v>-0.05945945945945946</v>
       </c>
       <c r="H4">
-        <v>-0.05977011494252873</v>
+        <v>-0.07027027027027026</v>
       </c>
       <c r="I4">
-        <v>-0.1887356321839081</v>
+        <v>-0.07567567567567568</v>
       </c>
       <c r="J4">
-        <v>-0.1887356321839081</v>
+        <v>-0.07567567567567568</v>
       </c>
       <c r="K4">
-        <v>-13.9</v>
+        <v>-0.012</v>
       </c>
       <c r="L4">
-        <v>-0.3195402298850575</v>
+        <v>-0.02162162162162162</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -886,73 +892,195 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.653</v>
+        <v>0.003</v>
       </c>
       <c r="V4">
-        <v>0.151508120649652</v>
+        <v>0.003128258602711158</v>
       </c>
       <c r="W4">
-        <v>0.2704280155642024</v>
+        <v>-0.02404809619238477</v>
       </c>
       <c r="X4">
-        <v>2.754616148910484</v>
+        <v>0.15748768748775</v>
       </c>
       <c r="Y4">
-        <v>-2.484188133346282</v>
+        <v>-0.1815357836801348</v>
       </c>
       <c r="Z4">
-        <v>1.899314500283805</v>
+        <v>1.137295081967213</v>
       </c>
       <c r="AA4">
-        <v>-0.3584683229271274</v>
+        <v>-0.08606557377049182</v>
       </c>
       <c r="AB4">
-        <v>0.2892367980393271</v>
+        <v>0.1573766058613267</v>
       </c>
       <c r="AC4">
-        <v>-0.6477051209664545</v>
+        <v>-0.2434421796318185</v>
       </c>
       <c r="AD4">
-        <v>78.7</v>
+        <v>0.003</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>78.7</v>
+        <v>0.003</v>
       </c>
       <c r="AG4">
-        <v>78.047</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>0.9480785447536442</v>
+        <v>0.003118503118503119</v>
       </c>
       <c r="AI4">
-        <v>5.917293233082709</v>
+        <v>0.01006711409395973</v>
       </c>
       <c r="AJ4">
-        <v>0.9476668649902255</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>6.171186842729505</v>
+        <v>0</v>
       </c>
       <c r="AL4">
-        <v>5.86</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>5.731</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>-30.26923076923077</v>
-      </c>
-      <c r="AO4">
-        <v>-1.401023890784983</v>
+        <v>-0.07692307692307693</v>
       </c>
       <c r="AP4">
-        <v>-30.01807692307692</v>
-      </c>
-      <c r="AQ4">
-        <v>-1.43255976269412</v>
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cocoa Processing Company Limited (GHSE:CPC)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Food Processing</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.0267</v>
+      </c>
+      <c r="G5">
+        <v>-0.1524844720496894</v>
+      </c>
+      <c r="H5">
+        <v>-0.1524844720496894</v>
+      </c>
+      <c r="I5">
+        <v>-0.3167701863354037</v>
+      </c>
+      <c r="J5">
+        <v>-0.3167701863354037</v>
+      </c>
+      <c r="K5">
+        <v>-11.5</v>
+      </c>
+      <c r="L5">
+        <v>-0.3571428571428571</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>2</v>
+      </c>
+      <c r="V5">
+        <v>0.5899705014749262</v>
+      </c>
+      <c r="W5">
+        <v>0.1965811965811966</v>
+      </c>
+      <c r="X5">
+        <v>1.545644249430767</v>
+      </c>
+      <c r="Y5">
+        <v>-1.349063052849571</v>
+      </c>
+      <c r="Z5">
+        <v>1.974854339159768</v>
+      </c>
+      <c r="AA5">
+        <v>-0.6255749770009202</v>
+      </c>
+      <c r="AB5">
+        <v>0.2074607585413775</v>
+      </c>
+      <c r="AC5">
+        <v>-0.8330357355422978</v>
+      </c>
+      <c r="AD5">
+        <v>53</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>53</v>
+      </c>
+      <c r="AG5">
+        <v>51</v>
+      </c>
+      <c r="AH5">
+        <v>0.9398829579712715</v>
+      </c>
+      <c r="AI5">
+        <v>0.8320251177394035</v>
+      </c>
+      <c r="AJ5">
+        <v>0.9376723662437948</v>
+      </c>
+      <c r="AK5">
+        <v>0.8265802269043759</v>
+      </c>
+      <c r="AL5">
+        <v>3.73</v>
+      </c>
+      <c r="AM5">
+        <v>1.33</v>
+      </c>
+      <c r="AN5">
+        <v>-10.79429735234216</v>
+      </c>
+      <c r="AO5">
+        <v>-2.734584450402144</v>
+      </c>
+      <c r="AP5">
+        <v>-10.38696537678208</v>
+      </c>
+      <c r="AQ5">
+        <v>-7.669172932330826</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/ghana/ghana_food_processing.xlsx
+++ b/research/traditional_assets/database/data/ghana/ghana_food_processing.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1464918932168536</v>
+        <v>0.1461594134838115</v>
       </c>
       <c r="C2">
-        <v>29.3</v>
+        <v>29.08796704029524</v>
       </c>
       <c r="D2">
-        <v>24.44</v>
+        <v>24.52096704029524</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.293</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.293</v>
       </c>
       <c r="G2">
         <v>4.86</v>
@@ -1579,28 +1579,28 @@
         <v>5.061</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0147379</v>
       </c>
       <c r="N2">
-        <v>5.061</v>
+        <v>5.0462621</v>
       </c>
       <c r="O2">
-        <v>1.26525</v>
+        <v>1.261565525</v>
       </c>
       <c r="P2">
-        <v>3.79575</v>
+        <v>3.784696575</v>
       </c>
       <c r="Q2">
-        <v>3.65475</v>
+        <v>3.643696575</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1464918932168536</v>
+        <v>0.1472547105897085</v>
       </c>
       <c r="T2">
-        <v>0.6158190843120042</v>
+        <v>0.6204843804052769</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>343.4003487606782</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1461594134838115</v>
+        <v>0.1458269337507693</v>
       </c>
       <c r="C3">
-        <v>29.08796704029524</v>
+        <v>28.8764723336176</v>
       </c>
       <c r="D3">
-        <v>24.52096704029524</v>
+        <v>24.60247233361759</v>
       </c>
       <c r="E3">
-        <v>0.293</v>
+        <v>0.5860000000000001</v>
       </c>
       <c r="F3">
-        <v>0.293</v>
+        <v>0.5860000000000001</v>
       </c>
       <c r="G3">
         <v>4.86</v>
@@ -1661,28 +1661,28 @@
         <v>5.061</v>
       </c>
       <c r="M3">
-        <v>0.0147379</v>
+        <v>0.0294758</v>
       </c>
       <c r="N3">
-        <v>5.0462621</v>
+        <v>5.0315242</v>
       </c>
       <c r="O3">
-        <v>1.261565525</v>
+        <v>1.25788105</v>
       </c>
       <c r="P3">
-        <v>3.784696575</v>
+        <v>3.77364315</v>
       </c>
       <c r="Q3">
-        <v>3.643696575</v>
+        <v>3.63264315</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1472547105897085</v>
+        <v>0.1480330956640503</v>
       </c>
       <c r="T3">
-        <v>0.6204843804052769</v>
+        <v>0.6252448866229022</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>343.4003487606782</v>
+        <v>171.7001743803391</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1458269337507693</v>
+        <v>0.1454944540177272</v>
       </c>
       <c r="C4">
-        <v>28.8764723336176</v>
+        <v>28.66552126516802</v>
       </c>
       <c r="D4">
-        <v>24.60247233361759</v>
+        <v>24.68452126516803</v>
       </c>
       <c r="E4">
-        <v>0.5860000000000001</v>
+        <v>0.879</v>
       </c>
       <c r="F4">
-        <v>0.5860000000000001</v>
+        <v>0.879</v>
       </c>
       <c r="G4">
         <v>4.86</v>
@@ -1743,28 +1743,28 @@
         <v>5.061</v>
       </c>
       <c r="M4">
-        <v>0.0294758</v>
+        <v>0.04421369999999999</v>
       </c>
       <c r="N4">
-        <v>5.0315242</v>
+        <v>5.0167863</v>
       </c>
       <c r="O4">
-        <v>1.25788105</v>
+        <v>1.254196575</v>
       </c>
       <c r="P4">
-        <v>3.77364315</v>
+        <v>3.762589725</v>
       </c>
       <c r="Q4">
-        <v>3.63264315</v>
+        <v>3.621589725</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1480330956640503</v>
+        <v>0.1488275299151827</v>
       </c>
       <c r="T4">
-        <v>0.6252448866229022</v>
+        <v>0.6301035476079011</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>171.7001743803391</v>
+        <v>114.4667829202261</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1454944540177272</v>
+        <v>0.1451619742846851</v>
       </c>
       <c r="C5">
-        <v>28.66552126516802</v>
+        <v>28.45511929222615</v>
       </c>
       <c r="D5">
-        <v>24.68452126516803</v>
+        <v>24.76711929222615</v>
       </c>
       <c r="E5">
-        <v>0.879</v>
+        <v>1.172</v>
       </c>
       <c r="F5">
-        <v>0.879</v>
+        <v>1.172</v>
       </c>
       <c r="G5">
         <v>4.86</v>
@@ -1825,28 +1825,28 @@
         <v>5.061</v>
       </c>
       <c r="M5">
-        <v>0.04421369999999999</v>
+        <v>0.05895160000000001</v>
       </c>
       <c r="N5">
-        <v>5.0167863</v>
+        <v>5.0020484</v>
       </c>
       <c r="O5">
-        <v>1.254196575</v>
+        <v>1.2505121</v>
       </c>
       <c r="P5">
-        <v>3.762589725</v>
+        <v>3.7515363</v>
       </c>
       <c r="Q5">
-        <v>3.621589725</v>
+        <v>3.6105363</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1488275299151827</v>
+        <v>0.1496385148798803</v>
       </c>
       <c r="T5">
-        <v>0.6301035476079011</v>
+        <v>0.6350634306967543</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>114.4667829202261</v>
+        <v>85.85008719016955</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1451619742846851</v>
+        <v>0.144829494551643</v>
       </c>
       <c r="C6">
-        <v>28.45511929222615</v>
+        <v>28.24527194536028</v>
       </c>
       <c r="D6">
-        <v>24.76711929222615</v>
+        <v>24.85027194536028</v>
       </c>
       <c r="E6">
-        <v>1.172</v>
+        <v>1.465</v>
       </c>
       <c r="F6">
-        <v>1.172</v>
+        <v>1.465</v>
       </c>
       <c r="G6">
         <v>4.86</v>
@@ -1907,28 +1907,28 @@
         <v>5.061</v>
       </c>
       <c r="M6">
-        <v>0.05895160000000001</v>
+        <v>0.0736895</v>
       </c>
       <c r="N6">
-        <v>5.0020484</v>
+        <v>4.9873105</v>
       </c>
       <c r="O6">
-        <v>1.2505121</v>
+        <v>1.246827625</v>
       </c>
       <c r="P6">
-        <v>3.7515363</v>
+        <v>3.740482875</v>
       </c>
       <c r="Q6">
-        <v>3.6105363</v>
+        <v>3.599482875</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1496385148798803</v>
+        <v>0.1504665732122557</v>
       </c>
       <c r="T6">
-        <v>0.6350634306967543</v>
+        <v>0.6401277323769518</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>85.85008719016955</v>
+        <v>68.68006975213564</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.144829494551643</v>
+        <v>0.1444970148186008</v>
       </c>
       <c r="C7">
-        <v>28.24527194536028</v>
+        <v>28.03598482966185</v>
       </c>
       <c r="D7">
-        <v>24.85027194536028</v>
+        <v>24.93398482966185</v>
       </c>
       <c r="E7">
-        <v>1.465</v>
+        <v>1.758</v>
       </c>
       <c r="F7">
-        <v>1.465</v>
+        <v>1.758</v>
       </c>
       <c r="G7">
         <v>4.86</v>
@@ -1989,28 +1989,28 @@
         <v>5.061</v>
       </c>
       <c r="M7">
-        <v>0.0736895</v>
+        <v>0.0884274</v>
       </c>
       <c r="N7">
-        <v>4.9873105</v>
+        <v>4.9725726</v>
       </c>
       <c r="O7">
-        <v>1.246827625</v>
+        <v>1.24314315</v>
       </c>
       <c r="P7">
-        <v>3.740482875</v>
+        <v>3.72942945</v>
       </c>
       <c r="Q7">
-        <v>3.599482875</v>
+        <v>3.58842945</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1504665732122557</v>
+        <v>0.1513122498070221</v>
       </c>
       <c r="T7">
-        <v>0.6401277323769518</v>
+        <v>0.6452997851567277</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>68.68006975213564</v>
+        <v>57.23339146011304</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1444970148186008</v>
+        <v>0.1441645350855587</v>
       </c>
       <c r="C8">
-        <v>28.03598482966185</v>
+        <v>27.82726362600477</v>
       </c>
       <c r="D8">
-        <v>24.93398482966185</v>
+        <v>25.01826362600477</v>
       </c>
       <c r="E8">
-        <v>1.758</v>
+        <v>2.051</v>
       </c>
       <c r="F8">
-        <v>1.758</v>
+        <v>2.051</v>
       </c>
       <c r="G8">
         <v>4.86</v>
@@ -2071,28 +2071,28 @@
         <v>5.061</v>
       </c>
       <c r="M8">
-        <v>0.08842739999999999</v>
+        <v>0.1031653</v>
       </c>
       <c r="N8">
-        <v>4.9725726</v>
+        <v>4.9578347</v>
       </c>
       <c r="O8">
-        <v>1.24314315</v>
+        <v>1.239458675</v>
       </c>
       <c r="P8">
-        <v>3.72942945</v>
+        <v>3.718376025</v>
       </c>
       <c r="Q8">
-        <v>3.58842945</v>
+        <v>3.577376025</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1513122498070221</v>
+        <v>0.1521761129952243</v>
       </c>
       <c r="T8">
-        <v>0.6452997851567277</v>
+        <v>0.6505830648780043</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>57.23339146011305</v>
+        <v>49.05719268009691</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1441645350855586</v>
+        <v>0.1438320553525165</v>
       </c>
       <c r="C9">
-        <v>27.82726362600477</v>
+        <v>27.61911409233071</v>
       </c>
       <c r="D9">
-        <v>25.01826362600477</v>
+        <v>25.10311409233071</v>
       </c>
       <c r="E9">
-        <v>2.051</v>
+        <v>2.344</v>
       </c>
       <c r="F9">
-        <v>2.051</v>
+        <v>2.344</v>
       </c>
       <c r="G9">
         <v>4.86</v>
@@ -2153,28 +2153,28 @@
         <v>5.061</v>
       </c>
       <c r="M9">
-        <v>0.1031653</v>
+        <v>0.1179032</v>
       </c>
       <c r="N9">
-        <v>4.9578347</v>
+        <v>4.9430968</v>
       </c>
       <c r="O9">
-        <v>1.239458675</v>
+        <v>1.2357742</v>
       </c>
       <c r="P9">
-        <v>3.718376025</v>
+        <v>3.7073226</v>
       </c>
       <c r="Q9">
-        <v>3.577376025</v>
+        <v>3.5663226</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1521761129952243</v>
+        <v>0.1530587558179528</v>
       </c>
       <c r="T9">
-        <v>0.6505830648780043</v>
+        <v>0.6559811985062654</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>49.0571926800969</v>
+        <v>42.92504359508478</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1438320553525165</v>
+        <v>0.1434995756194744</v>
       </c>
       <c r="C10">
-        <v>27.61911409233071</v>
+        <v>27.41154206496032</v>
       </c>
       <c r="D10">
-        <v>25.10311409233071</v>
+        <v>25.18854206496032</v>
       </c>
       <c r="E10">
-        <v>2.344</v>
+        <v>2.637</v>
       </c>
       <c r="F10">
-        <v>2.344</v>
+        <v>2.637</v>
       </c>
       <c r="G10">
         <v>4.86</v>
@@ -2235,28 +2235,28 @@
         <v>5.061</v>
       </c>
       <c r="M10">
-        <v>0.1179032</v>
+        <v>0.1326411</v>
       </c>
       <c r="N10">
-        <v>4.9430968</v>
+        <v>4.9283589</v>
       </c>
       <c r="O10">
-        <v>1.2357742</v>
+        <v>1.232089725</v>
       </c>
       <c r="P10">
-        <v>3.7073226</v>
+        <v>3.696269175</v>
       </c>
       <c r="Q10">
-        <v>3.5663226</v>
+        <v>3.555269175</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1530587558179528</v>
+        <v>0.1539607973840378</v>
       </c>
       <c r="T10">
-        <v>0.6559811985062654</v>
+        <v>0.6614979724340484</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>42.92504359508478</v>
+        <v>38.15559430674203</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1434995756194744</v>
+        <v>0.1431670958864323</v>
       </c>
       <c r="C11">
-        <v>27.41154206496032</v>
+        <v>27.20455345993144</v>
       </c>
       <c r="D11">
-        <v>25.18854206496032</v>
+        <v>25.27455345993144</v>
       </c>
       <c r="E11">
-        <v>2.637</v>
+        <v>2.93</v>
       </c>
       <c r="F11">
-        <v>2.637</v>
+        <v>2.93</v>
       </c>
       <c r="G11">
         <v>4.86</v>
@@ -2317,28 +2317,28 @@
         <v>5.061</v>
       </c>
       <c r="M11">
-        <v>0.1326411</v>
+        <v>0.147379</v>
       </c>
       <c r="N11">
-        <v>4.9283589</v>
+        <v>4.913621</v>
       </c>
       <c r="O11">
-        <v>1.232089725</v>
+        <v>1.22840525</v>
       </c>
       <c r="P11">
-        <v>3.696269175</v>
+        <v>3.68521575</v>
       </c>
       <c r="Q11">
-        <v>3.555269175</v>
+        <v>3.54421575</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1539607973840378</v>
+        <v>0.1548828843182581</v>
       </c>
       <c r="T11">
-        <v>0.6614979724340484</v>
+        <v>0.6671373413380045</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>38.15559430674203</v>
+        <v>34.34003487606783</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1431670958864323</v>
+        <v>0.1428346161533902</v>
       </c>
       <c r="C12">
-        <v>27.20455345993144</v>
+        <v>26.99815427436484</v>
       </c>
       <c r="D12">
-        <v>25.27455345993144</v>
+        <v>25.36115427436484</v>
       </c>
       <c r="E12">
-        <v>2.93</v>
+        <v>3.223</v>
       </c>
       <c r="F12">
-        <v>2.93</v>
+        <v>3.223</v>
       </c>
       <c r="G12">
         <v>4.86</v>
@@ -2399,28 +2399,28 @@
         <v>5.061</v>
       </c>
       <c r="M12">
-        <v>0.147379</v>
+        <v>0.1621169</v>
       </c>
       <c r="N12">
-        <v>4.913621</v>
+        <v>4.8988831</v>
       </c>
       <c r="O12">
-        <v>1.22840525</v>
+        <v>1.224720775</v>
       </c>
       <c r="P12">
-        <v>3.68521575</v>
+        <v>3.674162325</v>
       </c>
       <c r="Q12">
-        <v>3.54421575</v>
+        <v>3.533162325</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1548828843182581</v>
+        <v>0.1558256923071799</v>
       </c>
       <c r="T12">
-        <v>0.6671373413380045</v>
+        <v>0.6729034376330608</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>34.34003487606783</v>
+        <v>31.21821352369802</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1428346161533902</v>
+        <v>0.142502136420348</v>
       </c>
       <c r="C13">
-        <v>26.99815427436484</v>
+        <v>26.79235058785815</v>
       </c>
       <c r="D13">
-        <v>25.36115427436484</v>
+        <v>25.44835058785815</v>
       </c>
       <c r="E13">
-        <v>3.223</v>
+        <v>3.516</v>
       </c>
       <c r="F13">
-        <v>3.223</v>
+        <v>3.516</v>
       </c>
       <c r="G13">
         <v>4.86</v>
@@ -2481,28 +2481,28 @@
         <v>5.061</v>
       </c>
       <c r="M13">
-        <v>0.1621169</v>
+        <v>0.1768548</v>
       </c>
       <c r="N13">
-        <v>4.8988831</v>
+        <v>4.8841452</v>
       </c>
       <c r="O13">
-        <v>1.224720775</v>
+        <v>1.2210363</v>
       </c>
       <c r="P13">
-        <v>3.674162325</v>
+        <v>3.6631089</v>
       </c>
       <c r="Q13">
-        <v>3.533162325</v>
+        <v>3.5221089</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1558256923071799</v>
+        <v>0.1567899277503954</v>
       </c>
       <c r="T13">
-        <v>0.6729034376330608</v>
+        <v>0.6788005815711864</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>31.21821352369802</v>
+        <v>28.61669573005652</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.142502136420348</v>
+        <v>0.1421696566873059</v>
       </c>
       <c r="C14">
-        <v>26.79235058785815</v>
+        <v>26.58714856390851</v>
       </c>
       <c r="D14">
-        <v>25.44835058785815</v>
+        <v>25.53614856390852</v>
       </c>
       <c r="E14">
-        <v>3.516</v>
+        <v>3.809</v>
       </c>
       <c r="F14">
-        <v>3.516</v>
+        <v>3.809</v>
       </c>
       <c r="G14">
         <v>4.86</v>
@@ -2563,28 +2563,28 @@
         <v>5.061</v>
       </c>
       <c r="M14">
-        <v>0.1768548</v>
+        <v>0.1915927</v>
       </c>
       <c r="N14">
-        <v>4.8841452</v>
+        <v>4.8694073</v>
       </c>
       <c r="O14">
-        <v>1.2210363</v>
+        <v>1.217351825</v>
       </c>
       <c r="P14">
-        <v>3.6631089</v>
+        <v>3.652055475</v>
       </c>
       <c r="Q14">
-        <v>3.5221089</v>
+        <v>3.511055475</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1567899277503954</v>
+        <v>0.1577763295256389</v>
       </c>
       <c r="T14">
-        <v>0.6788005815711864</v>
+        <v>0.6848332920366252</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>28.61669573005652</v>
+        <v>26.41541144312909</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1421696566873059</v>
+        <v>0.1418371769542637</v>
       </c>
       <c r="C15">
-        <v>26.58714856390851</v>
+        <v>26.38255445136496</v>
       </c>
       <c r="D15">
-        <v>25.53614856390852</v>
+        <v>25.62455445136496</v>
       </c>
       <c r="E15">
-        <v>3.809</v>
+        <v>4.102</v>
       </c>
       <c r="F15">
-        <v>3.809</v>
+        <v>4.102</v>
       </c>
       <c r="G15">
         <v>4.86</v>
@@ -2645,28 +2645,28 @@
         <v>5.061</v>
       </c>
       <c r="M15">
-        <v>0.1915927</v>
+        <v>0.2063306</v>
       </c>
       <c r="N15">
-        <v>4.8694073</v>
+        <v>4.8546694</v>
       </c>
       <c r="O15">
-        <v>1.217351825</v>
+        <v>1.21366735</v>
       </c>
       <c r="P15">
-        <v>3.652055475</v>
+        <v>3.64100205</v>
       </c>
       <c r="Q15">
-        <v>3.511055475</v>
+        <v>3.50000205</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1577763295256389</v>
+        <v>0.1587856708770508</v>
       </c>
       <c r="T15">
-        <v>0.6848332920366252</v>
+        <v>0.6910062980942837</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>26.41541144312909</v>
+        <v>24.52859634004844</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1418371769542637</v>
+        <v>0.1415046972212216</v>
       </c>
       <c r="C16">
-        <v>26.38255445136496</v>
+        <v>26.17857458591091</v>
       </c>
       <c r="D16">
-        <v>25.62455445136496</v>
+        <v>25.71357458591091</v>
       </c>
       <c r="E16">
-        <v>4.102</v>
+        <v>4.395</v>
       </c>
       <c r="F16">
-        <v>4.102</v>
+        <v>4.395</v>
       </c>
       <c r="G16">
         <v>4.86</v>
@@ -2727,28 +2727,28 @@
         <v>5.061</v>
       </c>
       <c r="M16">
-        <v>0.2063306</v>
+        <v>0.2210685</v>
       </c>
       <c r="N16">
-        <v>4.8546694</v>
+        <v>4.8399315</v>
       </c>
       <c r="O16">
-        <v>1.21366735</v>
+        <v>1.209982875</v>
       </c>
       <c r="P16">
-        <v>3.64100205</v>
+        <v>3.629948625</v>
       </c>
       <c r="Q16">
-        <v>3.50000205</v>
+        <v>3.488948625</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1587856708770508</v>
+        <v>0.1598187614367313</v>
       </c>
       <c r="T16">
-        <v>0.6910062980942837</v>
+        <v>0.6973245513532988</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>24.52859634004844</v>
+        <v>22.89335658404521</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1415046972212216</v>
+        <v>0.1411722174881794</v>
       </c>
       <c r="C17">
-        <v>26.17857458591091</v>
+        <v>25.97521539157785</v>
       </c>
       <c r="D17">
-        <v>25.71357458591091</v>
+        <v>25.80321539157786</v>
       </c>
       <c r="E17">
-        <v>4.395</v>
+        <v>4.688000000000001</v>
       </c>
       <c r="F17">
-        <v>4.395</v>
+        <v>4.688000000000001</v>
       </c>
       <c r="G17">
         <v>4.86</v>
@@ -2809,28 +2809,28 @@
         <v>5.061</v>
       </c>
       <c r="M17">
-        <v>0.2210685</v>
+        <v>0.2358064</v>
       </c>
       <c r="N17">
-        <v>4.8399315</v>
+        <v>4.8251936</v>
       </c>
       <c r="O17">
-        <v>1.209982875</v>
+        <v>1.2062984</v>
       </c>
       <c r="P17">
-        <v>3.629948625</v>
+        <v>3.6188952</v>
       </c>
       <c r="Q17">
-        <v>3.488948625</v>
+        <v>3.4778952</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1598187614367313</v>
+        <v>0.1608764493906898</v>
       </c>
       <c r="T17">
-        <v>0.6973245513532988</v>
+        <v>0.7037932392137191</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>22.89335658404522</v>
+        <v>21.46252179754239</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1411722174881794</v>
+        <v>0.1408397377551373</v>
       </c>
       <c r="C18">
-        <v>25.97521539157785</v>
+        <v>25.77248338229057</v>
       </c>
       <c r="D18">
-        <v>25.80321539157786</v>
+        <v>25.89348338229057</v>
       </c>
       <c r="E18">
-        <v>4.688000000000001</v>
+        <v>4.981000000000001</v>
       </c>
       <c r="F18">
-        <v>4.688000000000001</v>
+        <v>4.981000000000001</v>
       </c>
       <c r="G18">
         <v>4.86</v>
@@ -2891,28 +2891,28 @@
         <v>5.061</v>
       </c>
       <c r="M18">
-        <v>0.2358064</v>
+        <v>0.2505443000000001</v>
       </c>
       <c r="N18">
-        <v>4.8251936</v>
+        <v>4.8104557</v>
       </c>
       <c r="O18">
-        <v>1.2062984</v>
+        <v>1.202613925</v>
       </c>
       <c r="P18">
-        <v>3.6188952</v>
+        <v>3.607841775</v>
       </c>
       <c r="Q18">
-        <v>3.4778952</v>
+        <v>3.466841775</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1608764493906898</v>
+        <v>0.1619596238013703</v>
       </c>
       <c r="T18">
-        <v>0.7037932392137191</v>
+        <v>0.710417799070776</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>21.46252179754239</v>
+        <v>20.20002051533401</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1408397377551373</v>
+        <v>0.1405072580220952</v>
       </c>
       <c r="C19">
-        <v>25.77248338229057</v>
+        <v>25.57038516344515</v>
       </c>
       <c r="D19">
-        <v>25.89348338229057</v>
+        <v>25.98438516344515</v>
       </c>
       <c r="E19">
-        <v>4.981000000000001</v>
+        <v>5.274000000000001</v>
       </c>
       <c r="F19">
-        <v>4.981000000000001</v>
+        <v>5.274000000000001</v>
       </c>
       <c r="G19">
         <v>4.86</v>
@@ -2973,28 +2973,28 @@
         <v>5.061</v>
       </c>
       <c r="M19">
-        <v>0.2505443000000001</v>
+        <v>0.2652822</v>
       </c>
       <c r="N19">
-        <v>4.8104557</v>
+        <v>4.7957178</v>
       </c>
       <c r="O19">
-        <v>1.202613925</v>
+        <v>1.19892945</v>
       </c>
       <c r="P19">
-        <v>3.607841775</v>
+        <v>3.59678835</v>
       </c>
       <c r="Q19">
-        <v>3.466841775</v>
+        <v>3.45578835</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1619596238013703</v>
+        <v>0.1630692171001161</v>
       </c>
       <c r="T19">
-        <v>0.710417799070776</v>
+        <v>0.7172039335584927</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>20.20002051533401</v>
+        <v>19.07779715337101</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1405072580220952</v>
+        <v>0.1401747782890531</v>
       </c>
       <c r="C20">
-        <v>25.57038516344515</v>
+        <v>25.36892743352017</v>
       </c>
       <c r="D20">
-        <v>25.98438516344515</v>
+        <v>26.07592743352017</v>
       </c>
       <c r="E20">
-        <v>5.274</v>
+        <v>5.567</v>
       </c>
       <c r="F20">
-        <v>5.274</v>
+        <v>5.567</v>
       </c>
       <c r="G20">
         <v>4.86</v>
@@ -3055,28 +3055,28 @@
         <v>5.061</v>
       </c>
       <c r="M20">
-        <v>0.2652822</v>
+        <v>0.2800201</v>
       </c>
       <c r="N20">
-        <v>4.7957178</v>
+        <v>4.7809799</v>
       </c>
       <c r="O20">
-        <v>1.19892945</v>
+        <v>1.195244975</v>
       </c>
       <c r="P20">
-        <v>3.59678835</v>
+        <v>3.585734925</v>
       </c>
       <c r="Q20">
-        <v>3.45578835</v>
+        <v>3.444734925</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1630692171001161</v>
+        <v>0.164206207764263</v>
       </c>
       <c r="T20">
-        <v>0.7172039335584927</v>
+        <v>0.7241576269224494</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>19.07779715337102</v>
+        <v>18.07370256635149</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1401747782890531</v>
+        <v>0.1398422985560109</v>
       </c>
       <c r="C21">
-        <v>25.36892743352017</v>
+        <v>25.16811698572214</v>
       </c>
       <c r="D21">
-        <v>26.07592743352017</v>
+        <v>26.16811698572214</v>
       </c>
       <c r="E21">
-        <v>5.567</v>
+        <v>5.86</v>
       </c>
       <c r="F21">
-        <v>5.567</v>
+        <v>5.86</v>
       </c>
       <c r="G21">
         <v>4.86</v>
@@ -3137,28 +3137,28 @@
         <v>5.061</v>
       </c>
       <c r="M21">
-        <v>0.2800201</v>
+        <v>0.294758</v>
       </c>
       <c r="N21">
-        <v>4.7809799</v>
+        <v>4.766242</v>
       </c>
       <c r="O21">
-        <v>1.195244975</v>
+        <v>1.1915605</v>
       </c>
       <c r="P21">
-        <v>3.585734925</v>
+        <v>3.5746815</v>
       </c>
       <c r="Q21">
-        <v>3.444734925</v>
+        <v>3.4336815</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.164206207764263</v>
+        <v>0.1653716231950136</v>
       </c>
       <c r="T21">
-        <v>0.7241576269224494</v>
+        <v>0.7312851626205049</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>18.07370256635149</v>
+        <v>17.17001743803391</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1398422985560109</v>
+        <v>0.1395098188229688</v>
       </c>
       <c r="C22">
-        <v>25.16811698572214</v>
+        <v>24.967960709666</v>
       </c>
       <c r="D22">
-        <v>26.16811698572214</v>
+        <v>26.260960709666</v>
       </c>
       <c r="E22">
-        <v>5.86</v>
+        <v>6.153</v>
       </c>
       <c r="F22">
-        <v>5.86</v>
+        <v>6.153</v>
       </c>
       <c r="G22">
         <v>4.86</v>
@@ -3219,28 +3219,28 @@
         <v>5.061</v>
       </c>
       <c r="M22">
-        <v>0.294758</v>
+        <v>0.3094959</v>
       </c>
       <c r="N22">
-        <v>4.766242</v>
+        <v>4.7515041</v>
       </c>
       <c r="O22">
-        <v>1.1915605</v>
+        <v>1.187876025</v>
       </c>
       <c r="P22">
-        <v>3.5746815</v>
+        <v>3.563628075</v>
       </c>
       <c r="Q22">
-        <v>3.4336815</v>
+        <v>3.422628075</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1653716231950136</v>
+        <v>0.1665665428138845</v>
       </c>
       <c r="T22">
-        <v>0.7312851626205049</v>
+        <v>0.7385931422602835</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>17.17001743803391</v>
+        <v>16.3523975600323</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1395098188229688</v>
+        <v>0.1391773390899266</v>
       </c>
       <c r="C23">
-        <v>24.967960709666</v>
+        <v>24.76846559309142</v>
       </c>
       <c r="D23">
-        <v>26.260960709666</v>
+        <v>26.35446559309142</v>
       </c>
       <c r="E23">
-        <v>6.153</v>
+        <v>6.446000000000001</v>
       </c>
       <c r="F23">
-        <v>6.153</v>
+        <v>6.446000000000001</v>
       </c>
       <c r="G23">
         <v>4.86</v>
@@ -3301,28 +3301,28 @@
         <v>5.061</v>
       </c>
       <c r="M23">
-        <v>0.3094959</v>
+        <v>0.3242338</v>
       </c>
       <c r="N23">
-        <v>4.7515041</v>
+        <v>4.7367662</v>
       </c>
       <c r="O23">
-        <v>1.187876025</v>
+        <v>1.18419155</v>
       </c>
       <c r="P23">
-        <v>3.563628075</v>
+        <v>3.55257465</v>
       </c>
       <c r="Q23">
-        <v>3.422628075</v>
+        <v>3.41157465</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1665665428138845</v>
+        <v>0.1677921013973419</v>
       </c>
       <c r="T23">
-        <v>0.7385931422602835</v>
+        <v>0.7460885059933896</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>16.3523975600323</v>
+        <v>15.60910676184901</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1391773390899266</v>
+        <v>0.1388448593568845</v>
       </c>
       <c r="C24">
-        <v>24.76846559309142</v>
+        <v>24.56963872361601</v>
       </c>
       <c r="D24">
-        <v>26.35446559309142</v>
+        <v>26.44863872361601</v>
       </c>
       <c r="E24">
-        <v>6.446000000000001</v>
+        <v>6.739000000000001</v>
       </c>
       <c r="F24">
-        <v>6.446000000000001</v>
+        <v>6.739000000000001</v>
       </c>
       <c r="G24">
         <v>4.86</v>
@@ -3383,28 +3383,28 @@
         <v>5.061</v>
       </c>
       <c r="M24">
-        <v>0.3242338</v>
+        <v>0.3389717</v>
       </c>
       <c r="N24">
-        <v>4.7367662</v>
+        <v>4.7220283</v>
       </c>
       <c r="O24">
-        <v>1.18419155</v>
+        <v>1.180507075</v>
       </c>
       <c r="P24">
-        <v>3.55257465</v>
+        <v>3.541521225</v>
       </c>
       <c r="Q24">
-        <v>3.41157465</v>
+        <v>3.400521225</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1677921013973419</v>
+        <v>0.1690494926712786</v>
       </c>
       <c r="T24">
-        <v>0.7460885059933896</v>
+        <v>0.7537785544987843</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>15.60910676184901</v>
+        <v>14.93044994611644</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1388448593568845</v>
+        <v>0.1385123796238424</v>
       </c>
       <c r="C25">
-        <v>24.56963872361601</v>
+        <v>24.37148729052622</v>
       </c>
       <c r="D25">
-        <v>26.44863872361601</v>
+        <v>26.54348729052622</v>
       </c>
       <c r="E25">
-        <v>6.739000000000001</v>
+        <v>7.032000000000001</v>
       </c>
       <c r="F25">
-        <v>6.739000000000001</v>
+        <v>7.032000000000001</v>
       </c>
       <c r="G25">
         <v>4.86</v>
@@ -3465,28 +3465,28 @@
         <v>5.061</v>
       </c>
       <c r="M25">
-        <v>0.3389717</v>
+        <v>0.3537096</v>
       </c>
       <c r="N25">
-        <v>4.7220283</v>
+        <v>4.7072904</v>
       </c>
       <c r="O25">
-        <v>1.180507075</v>
+        <v>1.1768226</v>
       </c>
       <c r="P25">
-        <v>3.541521225</v>
+        <v>3.5304678</v>
       </c>
       <c r="Q25">
-        <v>3.400521225</v>
+        <v>3.3894678</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1690494926712786</v>
+        <v>0.1703399731892663</v>
       </c>
       <c r="T25">
-        <v>0.7537785544987843</v>
+        <v>0.7616709727016894</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.93044994611644</v>
+        <v>14.30834786502826</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1385123796238424</v>
+        <v>0.1381798998908003</v>
       </c>
       <c r="C26">
-        <v>24.37148729052622</v>
+        <v>24.17401858660678</v>
       </c>
       <c r="D26">
-        <v>26.54348729052622</v>
+        <v>26.63901858660678</v>
       </c>
       <c r="E26">
-        <v>7.032</v>
+        <v>7.325</v>
       </c>
       <c r="F26">
-        <v>7.032</v>
+        <v>7.325</v>
       </c>
       <c r="G26">
         <v>4.86</v>
@@ -3547,28 +3547,28 @@
         <v>5.061</v>
       </c>
       <c r="M26">
-        <v>0.3537096</v>
+        <v>0.3684475</v>
       </c>
       <c r="N26">
-        <v>4.7072904</v>
+        <v>4.6925525</v>
       </c>
       <c r="O26">
-        <v>1.1768226</v>
+        <v>1.173138125</v>
       </c>
       <c r="P26">
-        <v>3.5304678</v>
+        <v>3.519414375</v>
       </c>
       <c r="Q26">
-        <v>3.3894678</v>
+        <v>3.378414375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1703399731892663</v>
+        <v>0.171664866521067</v>
       </c>
       <c r="T26">
-        <v>0.7616709727016894</v>
+        <v>0.7697738553900052</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>14.30834786502826</v>
+        <v>13.73601395042713</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1381798998908003</v>
+        <v>0.1378474201577581</v>
       </c>
       <c r="C27">
-        <v>24.17401858660678</v>
+        <v>23.97724001001006</v>
       </c>
       <c r="D27">
-        <v>26.63901858660678</v>
+        <v>26.73524001001006</v>
       </c>
       <c r="E27">
-        <v>7.325</v>
+        <v>7.618</v>
       </c>
       <c r="F27">
-        <v>7.325</v>
+        <v>7.618</v>
       </c>
       <c r="G27">
         <v>4.86</v>
@@ -3629,28 +3629,28 @@
         <v>5.061</v>
       </c>
       <c r="M27">
-        <v>0.3684475</v>
+        <v>0.3831854</v>
       </c>
       <c r="N27">
-        <v>4.6925525</v>
+        <v>4.6778146</v>
       </c>
       <c r="O27">
-        <v>1.173138125</v>
+        <v>1.16945365</v>
       </c>
       <c r="P27">
-        <v>3.519414375</v>
+        <v>3.50836095</v>
       </c>
       <c r="Q27">
-        <v>3.378414375</v>
+        <v>3.36736095</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.171664866521067</v>
+        <v>0.1730255677807542</v>
       </c>
       <c r="T27">
-        <v>0.7697738553900052</v>
+        <v>0.7780957349077351</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>13.73601395042713</v>
+        <v>13.20770572156455</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1378474201577581</v>
+        <v>0.137818690424716</v>
       </c>
       <c r="C28">
-        <v>23.97724001001006</v>
+        <v>23.69258718714071</v>
       </c>
       <c r="D28">
-        <v>26.73524001001006</v>
+        <v>26.74358718714071</v>
       </c>
       <c r="E28">
-        <v>7.618</v>
+        <v>7.911</v>
       </c>
       <c r="F28">
-        <v>7.618</v>
+        <v>7.911</v>
       </c>
       <c r="G28">
         <v>4.86</v>
@@ -3711,45 +3711,45 @@
         <v>5.061</v>
       </c>
       <c r="M28">
-        <v>0.3831854</v>
+        <v>0.4097898</v>
       </c>
       <c r="N28">
-        <v>4.6778146</v>
+        <v>4.6512102</v>
       </c>
       <c r="O28">
-        <v>1.16945365</v>
+        <v>1.16280255</v>
       </c>
       <c r="P28">
-        <v>3.50836095</v>
+        <v>3.48840765</v>
       </c>
       <c r="Q28">
-        <v>3.36736095</v>
+        <v>3.34740765</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1730255677807542</v>
+        <v>0.1744235485270082</v>
       </c>
       <c r="T28">
-        <v>0.7780957349077351</v>
+        <v>0.7866456111245808</v>
       </c>
       <c r="U28">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y28">
-        <v>13.20770572156455</v>
+        <v>12.3502341932376</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.137818690424716</v>
+        <v>0.1374974606916738</v>
       </c>
       <c r="C29">
-        <v>23.69258718714071</v>
+        <v>23.49327391857159</v>
       </c>
       <c r="D29">
-        <v>26.74358718714071</v>
+        <v>26.83727391857159</v>
       </c>
       <c r="E29">
-        <v>7.911</v>
+        <v>8.204000000000001</v>
       </c>
       <c r="F29">
-        <v>7.911</v>
+        <v>8.204000000000001</v>
       </c>
       <c r="G29">
         <v>4.86</v>
@@ -3793,28 +3793,28 @@
         <v>5.061</v>
       </c>
       <c r="M29">
-        <v>0.4097898</v>
+        <v>0.4249672</v>
       </c>
       <c r="N29">
-        <v>4.6512102</v>
+        <v>4.6360328</v>
       </c>
       <c r="O29">
-        <v>1.16280255</v>
+        <v>1.1590082</v>
       </c>
       <c r="P29">
-        <v>3.48840765</v>
+        <v>3.4770246</v>
       </c>
       <c r="Q29">
-        <v>3.34740765</v>
+        <v>3.3360246</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1744235485270082</v>
+        <v>0.1758603620717692</v>
       </c>
       <c r="T29">
-        <v>0.7866456111245808</v>
+        <v>0.7954329839030054</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>12.3502341932376</v>
+        <v>11.90915440062198</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1374974606916738</v>
+        <v>0.1371762309586317</v>
       </c>
       <c r="C30">
-        <v>23.49327391857159</v>
+        <v>23.29461935442508</v>
       </c>
       <c r="D30">
-        <v>26.83727391857159</v>
+        <v>26.93161935442508</v>
       </c>
       <c r="E30">
-        <v>8.204000000000001</v>
+        <v>8.497000000000002</v>
       </c>
       <c r="F30">
-        <v>8.204000000000001</v>
+        <v>8.497000000000002</v>
       </c>
       <c r="G30">
         <v>4.86</v>
@@ -3875,28 +3875,28 @@
         <v>5.061</v>
       </c>
       <c r="M30">
-        <v>0.4249672</v>
+        <v>0.4401446000000001</v>
       </c>
       <c r="N30">
-        <v>4.6360328</v>
+        <v>4.6208554</v>
       </c>
       <c r="O30">
-        <v>1.1590082</v>
+        <v>1.15521385</v>
       </c>
       <c r="P30">
-        <v>3.4770246</v>
+        <v>3.46564155</v>
       </c>
       <c r="Q30">
-        <v>3.3360246</v>
+        <v>3.32464155</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1758603620717692</v>
+        <v>0.1773376492375094</v>
       </c>
       <c r="T30">
-        <v>0.7954329839030054</v>
+        <v>0.8044678883089913</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.90915440062198</v>
+        <v>11.4984939040488</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1371762309586317</v>
+        <v>0.1368550012255896</v>
       </c>
       <c r="C31">
-        <v>23.29461935442509</v>
+        <v>23.09663046616162</v>
       </c>
       <c r="D31">
-        <v>26.93161935442509</v>
+        <v>27.02663046616162</v>
       </c>
       <c r="E31">
-        <v>8.497</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="F31">
-        <v>8.497</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G31">
         <v>4.86</v>
@@ -3957,28 +3957,28 @@
         <v>5.061</v>
       </c>
       <c r="M31">
-        <v>0.4401446</v>
+        <v>0.4553219999999999</v>
       </c>
       <c r="N31">
-        <v>4.6208554</v>
+        <v>4.605678</v>
       </c>
       <c r="O31">
-        <v>1.15521385</v>
+        <v>1.1514195</v>
       </c>
       <c r="P31">
-        <v>3.46564155</v>
+        <v>3.4542585</v>
       </c>
       <c r="Q31">
-        <v>3.32464155</v>
+        <v>3.3132585</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1773376492375094</v>
+        <v>0.1788571446079851</v>
       </c>
       <c r="T31">
-        <v>0.8044678883089913</v>
+        <v>0.8137609328408626</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.49849390404881</v>
+        <v>11.11521077391385</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1368550012255896</v>
+        <v>0.1365337714925474</v>
       </c>
       <c r="C32">
-        <v>23.09663046616162</v>
+        <v>22.89931432396738</v>
       </c>
       <c r="D32">
-        <v>27.02663046616162</v>
+        <v>27.12231432396738</v>
       </c>
       <c r="E32">
-        <v>8.789999999999999</v>
+        <v>9.083</v>
       </c>
       <c r="F32">
-        <v>8.789999999999999</v>
+        <v>9.083</v>
       </c>
       <c r="G32">
         <v>4.86</v>
@@ -4039,28 +4039,28 @@
         <v>5.061</v>
       </c>
       <c r="M32">
-        <v>0.4553219999999999</v>
+        <v>0.4704994</v>
       </c>
       <c r="N32">
-        <v>4.605678</v>
+        <v>4.5905006</v>
       </c>
       <c r="O32">
-        <v>1.1514195</v>
+        <v>1.14762515</v>
       </c>
       <c r="P32">
-        <v>3.4542585</v>
+        <v>3.44287545</v>
       </c>
       <c r="Q32">
-        <v>3.3132585</v>
+        <v>3.30187545</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1788571446079851</v>
+        <v>0.1804206833225325</v>
       </c>
       <c r="T32">
-        <v>0.8137609328408626</v>
+        <v>0.8233233409823534</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.11521077391385</v>
+        <v>10.75665558765856</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1365337714925474</v>
+        <v>0.1362125417595053</v>
       </c>
       <c r="C33">
-        <v>22.89931432396738</v>
+        <v>22.70267809850816</v>
       </c>
       <c r="D33">
-        <v>27.12231432396738</v>
+        <v>27.21867809850816</v>
       </c>
       <c r="E33">
-        <v>9.083</v>
+        <v>9.376000000000001</v>
       </c>
       <c r="F33">
-        <v>9.083</v>
+        <v>9.376000000000001</v>
       </c>
       <c r="G33">
         <v>4.86</v>
@@ -4121,28 +4121,28 @@
         <v>5.061</v>
       </c>
       <c r="M33">
-        <v>0.4704994</v>
+        <v>0.4856768000000001</v>
       </c>
       <c r="N33">
-        <v>4.5905006</v>
+        <v>4.5753232</v>
       </c>
       <c r="O33">
-        <v>1.14762515</v>
+        <v>1.1438308</v>
       </c>
       <c r="P33">
-        <v>3.44287545</v>
+        <v>3.4314924</v>
       </c>
       <c r="Q33">
-        <v>3.30187545</v>
+        <v>3.2904924</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1804206833225325</v>
+        <v>0.1820302084698608</v>
       </c>
       <c r="T33">
-        <v>0.8233233409823534</v>
+        <v>0.8331669964221233</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.75665558765856</v>
+        <v>10.42051010054423</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1362125417595053</v>
+        <v>0.1358913120264632</v>
       </c>
       <c r="C34">
-        <v>22.70267809850816</v>
+        <v>22.50672906272073</v>
       </c>
       <c r="D34">
-        <v>27.21867809850816</v>
+        <v>27.31572906272073</v>
       </c>
       <c r="E34">
-        <v>9.376000000000001</v>
+        <v>9.669</v>
       </c>
       <c r="F34">
-        <v>9.376000000000001</v>
+        <v>9.669</v>
       </c>
       <c r="G34">
         <v>4.86</v>
@@ -4203,28 +4203,28 @@
         <v>5.061</v>
       </c>
       <c r="M34">
-        <v>0.4856768000000001</v>
+        <v>0.5008542</v>
       </c>
       <c r="N34">
-        <v>4.5753232</v>
+        <v>4.5601458</v>
       </c>
       <c r="O34">
-        <v>1.1438308</v>
+        <v>1.14003645</v>
       </c>
       <c r="P34">
-        <v>3.4314924</v>
+        <v>3.42010935</v>
       </c>
       <c r="Q34">
-        <v>3.2904924</v>
+        <v>3.27910935</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1820302084698608</v>
+        <v>0.1836877791439749</v>
       </c>
       <c r="T34">
-        <v>0.8331669964221233</v>
+        <v>0.8433044923227819</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.42051010054423</v>
+        <v>10.1047370671944</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1358913120264632</v>
+        <v>0.136003582293421</v>
       </c>
       <c r="C35">
-        <v>22.50672906272073</v>
+        <v>22.17973103164427</v>
       </c>
       <c r="D35">
-        <v>27.31572906272073</v>
+        <v>27.28173103164427</v>
       </c>
       <c r="E35">
-        <v>9.669</v>
+        <v>9.962000000000002</v>
       </c>
       <c r="F35">
-        <v>9.669</v>
+        <v>9.962000000000002</v>
       </c>
       <c r="G35">
         <v>4.86</v>
@@ -4285,45 +4285,45 @@
         <v>5.061</v>
       </c>
       <c r="M35">
-        <v>0.5008542</v>
+        <v>0.5329670000000001</v>
       </c>
       <c r="N35">
-        <v>4.5601458</v>
+        <v>4.528033</v>
       </c>
       <c r="O35">
-        <v>1.14003645</v>
+        <v>1.13200825</v>
       </c>
       <c r="P35">
-        <v>3.42010935</v>
+        <v>3.39602475</v>
       </c>
       <c r="Q35">
-        <v>3.27910935</v>
+        <v>3.25502475</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1836877791439749</v>
+        <v>0.1853955792324561</v>
       </c>
       <c r="T35">
-        <v>0.8433044923227819</v>
+        <v>0.853749185068915</v>
       </c>
       <c r="U35">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>10.1047370671944</v>
+        <v>9.495897494591595</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.136003582293421</v>
+        <v>0.1356951025603789</v>
       </c>
       <c r="C36">
-        <v>22.17973103164427</v>
+        <v>21.98034971459662</v>
       </c>
       <c r="D36">
-        <v>27.28173103164427</v>
+        <v>27.37534971459662</v>
       </c>
       <c r="E36">
-        <v>9.962000000000002</v>
+        <v>10.255</v>
       </c>
       <c r="F36">
-        <v>9.962000000000002</v>
+        <v>10.255</v>
       </c>
       <c r="G36">
         <v>4.86</v>
@@ -4367,28 +4367,28 @@
         <v>5.061</v>
       </c>
       <c r="M36">
-        <v>0.5329670000000001</v>
+        <v>0.5486425</v>
       </c>
       <c r="N36">
-        <v>4.528033</v>
+        <v>4.5123575</v>
       </c>
       <c r="O36">
-        <v>1.13200825</v>
+        <v>1.128089375</v>
       </c>
       <c r="P36">
-        <v>3.39602475</v>
+        <v>3.384268125</v>
       </c>
       <c r="Q36">
-        <v>3.25502475</v>
+        <v>3.243268125</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1853955792324561</v>
+        <v>0.1871559270159676</v>
       </c>
       <c r="T36">
-        <v>0.853749185068915</v>
+        <v>0.8645152529764675</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>9.495897494591595</v>
+        <v>9.224586137603266</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1356951025603789</v>
+        <v>0.1353866228273368</v>
       </c>
       <c r="C37">
-        <v>21.98034971459662</v>
+        <v>21.78161312475071</v>
       </c>
       <c r="D37">
-        <v>27.37534971459662</v>
+        <v>27.46961312475072</v>
       </c>
       <c r="E37">
-        <v>10.255</v>
+        <v>10.548</v>
       </c>
       <c r="F37">
-        <v>10.255</v>
+        <v>10.548</v>
       </c>
       <c r="G37">
         <v>4.86</v>
@@ -4449,28 +4449,28 @@
         <v>5.061</v>
       </c>
       <c r="M37">
-        <v>0.5486425</v>
+        <v>0.5643180000000001</v>
       </c>
       <c r="N37">
-        <v>4.5123575</v>
+        <v>4.496682</v>
       </c>
       <c r="O37">
-        <v>1.128089375</v>
+        <v>1.1241705</v>
       </c>
       <c r="P37">
-        <v>3.384268125</v>
+        <v>3.3725115</v>
       </c>
       <c r="Q37">
-        <v>3.243268125</v>
+        <v>3.2315115</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1871559270159676</v>
+        <v>0.1889712856677137</v>
       </c>
       <c r="T37">
-        <v>0.8645152529764675</v>
+        <v>0.8756177605061309</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>9.224586137603266</v>
+        <v>8.968347633780951</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1353866228273368</v>
+        <v>0.1350781430942946</v>
       </c>
       <c r="C38">
-        <v>21.78161312475071</v>
+        <v>21.58352794521852</v>
       </c>
       <c r="D38">
-        <v>27.46961312475072</v>
+        <v>27.56452794521852</v>
       </c>
       <c r="E38">
-        <v>10.548</v>
+        <v>10.841</v>
       </c>
       <c r="F38">
-        <v>10.548</v>
+        <v>10.841</v>
       </c>
       <c r="G38">
         <v>4.86</v>
@@ -4531,28 +4531,28 @@
         <v>5.061</v>
       </c>
       <c r="M38">
-        <v>0.564318</v>
+        <v>0.5799934999999999</v>
       </c>
       <c r="N38">
-        <v>4.496682</v>
+        <v>4.4810065</v>
       </c>
       <c r="O38">
-        <v>1.1241705</v>
+        <v>1.120251625</v>
       </c>
       <c r="P38">
-        <v>3.3725115</v>
+        <v>3.360754875</v>
       </c>
       <c r="Q38">
-        <v>3.2315115</v>
+        <v>3.219754875</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1889712856677137</v>
+        <v>0.1908442747528487</v>
       </c>
       <c r="T38">
-        <v>0.8756177605061309</v>
+        <v>0.8870727285922917</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.968347633780954</v>
+        <v>8.725959859894983</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1350781430942946</v>
+        <v>0.1347696633612525</v>
       </c>
       <c r="C39">
-        <v>21.58352794521852</v>
+        <v>21.38610095179995</v>
       </c>
       <c r="D39">
-        <v>27.56452794521852</v>
+        <v>27.66010095179995</v>
       </c>
       <c r="E39">
-        <v>10.841</v>
+        <v>11.134</v>
       </c>
       <c r="F39">
-        <v>10.841</v>
+        <v>11.134</v>
       </c>
       <c r="G39">
         <v>4.86</v>
@@ -4613,28 +4613,28 @@
         <v>5.061</v>
       </c>
       <c r="M39">
-        <v>0.5799934999999999</v>
+        <v>0.595669</v>
       </c>
       <c r="N39">
-        <v>4.4810065</v>
+        <v>4.465331</v>
       </c>
       <c r="O39">
-        <v>1.120251625</v>
+        <v>1.11633275</v>
       </c>
       <c r="P39">
-        <v>3.360754875</v>
+        <v>3.34899825</v>
       </c>
       <c r="Q39">
-        <v>3.219754875</v>
+        <v>3.20799825</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1908442747528487</v>
+        <v>0.1927776828407299</v>
       </c>
       <c r="T39">
-        <v>0.8870727285922917</v>
+        <v>0.8988972117780061</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.725959859894983</v>
+        <v>8.496329337266166</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1347696633612525</v>
+        <v>0.1344611836282104</v>
       </c>
       <c r="C40">
-        <v>21.38610095179995</v>
+        <v>21.18933901459539</v>
       </c>
       <c r="D40">
-        <v>27.66010095179995</v>
+        <v>27.75633901459539</v>
       </c>
       <c r="E40">
-        <v>11.134</v>
+        <v>11.427</v>
       </c>
       <c r="F40">
-        <v>11.134</v>
+        <v>11.427</v>
       </c>
       <c r="G40">
         <v>4.86</v>
@@ -4695,28 +4695,28 @@
         <v>5.061</v>
       </c>
       <c r="M40">
-        <v>0.595669</v>
+        <v>0.6113445000000001</v>
       </c>
       <c r="N40">
-        <v>4.465331</v>
+        <v>4.4496555</v>
       </c>
       <c r="O40">
-        <v>1.11633275</v>
+        <v>1.112413875</v>
       </c>
       <c r="P40">
-        <v>3.34899825</v>
+        <v>3.337241625</v>
       </c>
       <c r="Q40">
-        <v>3.20799825</v>
+        <v>3.196241625</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1927776828407299</v>
+        <v>0.1947744813577219</v>
       </c>
       <c r="T40">
-        <v>0.8988972117780061</v>
+        <v>0.9111093829370226</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.496329337266166</v>
+        <v>8.278474738874724</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1344611836282104</v>
+        <v>0.1341527038951683</v>
       </c>
       <c r="C41">
-        <v>21.18933901459539</v>
+        <v>20.99324909965186</v>
       </c>
       <c r="D41">
-        <v>27.75633901459539</v>
+        <v>27.85324909965186</v>
       </c>
       <c r="E41">
-        <v>11.427</v>
+        <v>11.72</v>
       </c>
       <c r="F41">
-        <v>11.427</v>
+        <v>11.72</v>
       </c>
       <c r="G41">
         <v>4.86</v>
@@ -4777,28 +4777,28 @@
         <v>5.061</v>
       </c>
       <c r="M41">
-        <v>0.6113445000000001</v>
+        <v>0.62702</v>
       </c>
       <c r="N41">
-        <v>4.4496555</v>
+        <v>4.43398</v>
       </c>
       <c r="O41">
-        <v>1.112413875</v>
+        <v>1.108495</v>
       </c>
       <c r="P41">
-        <v>3.337241625</v>
+        <v>3.325485</v>
       </c>
       <c r="Q41">
-        <v>3.196241625</v>
+        <v>3.184485</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1947744813577219</v>
+        <v>0.1968378398252804</v>
       </c>
       <c r="T41">
-        <v>0.9111093829370226</v>
+        <v>0.9237286264680062</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.278474738874724</v>
+        <v>8.071512870402858</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1341527038951683</v>
+        <v>0.1338442241621261</v>
       </c>
       <c r="C42">
-        <v>20.99324909965186</v>
+        <v>20.79783827064386</v>
       </c>
       <c r="D42">
-        <v>27.85324909965186</v>
+        <v>27.95083827064386</v>
       </c>
       <c r="E42">
-        <v>11.72</v>
+        <v>12.013</v>
       </c>
       <c r="F42">
-        <v>11.72</v>
+        <v>12.013</v>
       </c>
       <c r="G42">
         <v>4.86</v>
@@ -4859,28 +4859,28 @@
         <v>5.061</v>
       </c>
       <c r="M42">
-        <v>0.62702</v>
+        <v>0.6426955000000001</v>
       </c>
       <c r="N42">
-        <v>4.43398</v>
+        <v>4.4183045</v>
       </c>
       <c r="O42">
-        <v>1.108495</v>
+        <v>1.104576125</v>
       </c>
       <c r="P42">
-        <v>3.325485</v>
+        <v>3.313728375</v>
       </c>
       <c r="Q42">
-        <v>3.184485</v>
+        <v>3.172728375</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1968378398252804</v>
+        <v>0.1989711426476714</v>
       </c>
       <c r="T42">
-        <v>0.9237286264680062</v>
+        <v>0.9367756409661421</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.071512870402858</v>
+        <v>7.874646702832055</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1338442241621261</v>
+        <v>0.133535744429084</v>
       </c>
       <c r="C43">
-        <v>20.79783827064386</v>
+        <v>20.60311369058975</v>
       </c>
       <c r="D43">
-        <v>27.95083827064386</v>
+        <v>28.04911369058975</v>
       </c>
       <c r="E43">
-        <v>12.013</v>
+        <v>12.306</v>
       </c>
       <c r="F43">
-        <v>12.013</v>
+        <v>12.306</v>
       </c>
       <c r="G43">
         <v>4.86</v>
@@ -4941,28 +4941,28 @@
         <v>5.061</v>
       </c>
       <c r="M43">
-        <v>0.6426955000000001</v>
+        <v>0.658371</v>
       </c>
       <c r="N43">
-        <v>4.4183045</v>
+        <v>4.402629</v>
       </c>
       <c r="O43">
-        <v>1.104576125</v>
+        <v>1.10065725</v>
       </c>
       <c r="P43">
-        <v>3.313728375</v>
+        <v>3.30197175</v>
       </c>
       <c r="Q43">
-        <v>3.172728375</v>
+        <v>3.16097175</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1989711426476714</v>
+        <v>0.2011780076363517</v>
       </c>
       <c r="T43">
-        <v>0.9367756409661421</v>
+        <v>0.9502725525159375</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.874646702832055</v>
+        <v>7.687155114669388</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.133535744429084</v>
+        <v>0.1334852646960419</v>
       </c>
       <c r="C44">
-        <v>20.60311369058974</v>
+        <v>20.3262613497897</v>
       </c>
       <c r="D44">
-        <v>28.04911369058973</v>
+        <v>28.0652613497897</v>
       </c>
       <c r="E44">
-        <v>12.306</v>
+        <v>12.599</v>
       </c>
       <c r="F44">
-        <v>12.306</v>
+        <v>12.599</v>
       </c>
       <c r="G44">
         <v>4.86</v>
@@ -5023,45 +5023,45 @@
         <v>5.061</v>
       </c>
       <c r="M44">
-        <v>0.6583709999999999</v>
+        <v>0.6841257000000001</v>
       </c>
       <c r="N44">
-        <v>4.402629</v>
+        <v>4.3768743</v>
       </c>
       <c r="O44">
-        <v>1.10065725</v>
+        <v>1.094218575</v>
       </c>
       <c r="P44">
-        <v>3.30197175</v>
+        <v>3.282655725</v>
       </c>
       <c r="Q44">
-        <v>3.16097175</v>
+        <v>3.141655725</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2011780076363517</v>
+        <v>0.2034623064842839</v>
       </c>
       <c r="T44">
-        <v>0.9502725525159375</v>
+        <v>0.9642430399095854</v>
       </c>
       <c r="U44">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y44">
-        <v>7.687155114669389</v>
+        <v>7.397763305778455</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1334852646960419</v>
+        <v>0.1331827849629997</v>
       </c>
       <c r="C45">
-        <v>20.3262613497897</v>
+        <v>20.13041060824417</v>
       </c>
       <c r="D45">
-        <v>28.0652613497897</v>
+        <v>28.16241060824417</v>
       </c>
       <c r="E45">
-        <v>12.599</v>
+        <v>12.892</v>
       </c>
       <c r="F45">
-        <v>12.599</v>
+        <v>12.892</v>
       </c>
       <c r="G45">
         <v>4.86</v>
@@ -5105,28 +5105,28 @@
         <v>5.061</v>
       </c>
       <c r="M45">
-        <v>0.6841257000000001</v>
+        <v>0.7000356000000001</v>
       </c>
       <c r="N45">
-        <v>4.3768743</v>
+        <v>4.3609644</v>
       </c>
       <c r="O45">
-        <v>1.094218575</v>
+        <v>1.0902411</v>
       </c>
       <c r="P45">
-        <v>3.282655725</v>
+        <v>3.2707233</v>
       </c>
       <c r="Q45">
-        <v>3.141655725</v>
+        <v>3.1297233</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2034623064842839</v>
+        <v>0.2058281874339281</v>
       </c>
       <c r="T45">
-        <v>0.9642430399095854</v>
+        <v>0.9787124732815781</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.397763305778455</v>
+        <v>7.229632321556218</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1331827849629997</v>
+        <v>0.1328803052299576</v>
       </c>
       <c r="C46">
-        <v>20.13041060824417</v>
+        <v>19.93523477663804</v>
       </c>
       <c r="D46">
-        <v>28.16241060824417</v>
+        <v>28.26023477663804</v>
       </c>
       <c r="E46">
-        <v>12.892</v>
+        <v>13.185</v>
       </c>
       <c r="F46">
-        <v>12.892</v>
+        <v>13.185</v>
       </c>
       <c r="G46">
         <v>4.86</v>
@@ -5187,28 +5187,28 @@
         <v>5.061</v>
       </c>
       <c r="M46">
-        <v>0.7000356000000001</v>
+        <v>0.7159455</v>
       </c>
       <c r="N46">
-        <v>4.3609644</v>
+        <v>4.3450545</v>
       </c>
       <c r="O46">
-        <v>1.0902411</v>
+        <v>1.086263625</v>
       </c>
       <c r="P46">
-        <v>3.2707233</v>
+        <v>3.258790875</v>
       </c>
       <c r="Q46">
-        <v>3.1297233</v>
+        <v>3.117790875</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2058281874339281</v>
+        <v>0.2082801004181047</v>
       </c>
       <c r="T46">
-        <v>0.9787124732815781</v>
+        <v>0.9937080678670975</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>7.229632321556218</v>
+        <v>7.068973825521635</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1328803052299576</v>
+        <v>0.1325778254969154</v>
       </c>
       <c r="C47">
-        <v>19.93523477663804</v>
+        <v>19.74074091253159</v>
       </c>
       <c r="D47">
-        <v>28.26023477663804</v>
+        <v>28.35874091253158</v>
       </c>
       <c r="E47">
-        <v>13.185</v>
+        <v>13.478</v>
       </c>
       <c r="F47">
-        <v>13.185</v>
+        <v>13.478</v>
       </c>
       <c r="G47">
         <v>4.86</v>
@@ -5269,28 +5269,28 @@
         <v>5.061</v>
       </c>
       <c r="M47">
-        <v>0.7159455</v>
+        <v>0.7318554</v>
       </c>
       <c r="N47">
-        <v>4.3450545</v>
+        <v>4.3291446</v>
       </c>
       <c r="O47">
-        <v>1.086263625</v>
+        <v>1.08228615</v>
       </c>
       <c r="P47">
-        <v>3.258790875</v>
+        <v>3.24685845</v>
       </c>
       <c r="Q47">
-        <v>3.117790875</v>
+        <v>3.10585845</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2082801004181047</v>
+        <v>0.2108228249942878</v>
       </c>
       <c r="T47">
-        <v>0.9937080678670975</v>
+        <v>1.009259054844673</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.068973825521635</v>
+        <v>6.915300481488556</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1325778254969154</v>
+        <v>0.1322753457638733</v>
       </c>
       <c r="C48">
-        <v>19.74074091253159</v>
+        <v>19.54693617223087</v>
       </c>
       <c r="D48">
-        <v>28.35874091253158</v>
+        <v>28.45793617223087</v>
       </c>
       <c r="E48">
-        <v>13.478</v>
+        <v>13.771</v>
       </c>
       <c r="F48">
-        <v>13.478</v>
+        <v>13.771</v>
       </c>
       <c r="G48">
         <v>4.86</v>
@@ -5351,28 +5351,28 @@
         <v>5.061</v>
       </c>
       <c r="M48">
-        <v>0.7318554</v>
+        <v>0.7477653000000001</v>
       </c>
       <c r="N48">
-        <v>4.3291446</v>
+        <v>4.3132347</v>
       </c>
       <c r="O48">
-        <v>1.08228615</v>
+        <v>1.078308675</v>
       </c>
       <c r="P48">
-        <v>3.24685845</v>
+        <v>3.234926025</v>
       </c>
       <c r="Q48">
-        <v>3.10585845</v>
+        <v>3.093926025</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2108228249942878</v>
+        <v>0.2134615014412704</v>
       </c>
       <c r="T48">
-        <v>1.009259054844673</v>
+        <v>1.025396871519516</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.915300481488556</v>
+        <v>6.768166428690926</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1322753457638733</v>
+        <v>0.1319728660308312</v>
       </c>
       <c r="C49">
-        <v>19.54693617223087</v>
+        <v>19.35382781252083</v>
       </c>
       <c r="D49">
-        <v>28.45793617223087</v>
+        <v>28.55782781252083</v>
       </c>
       <c r="E49">
-        <v>13.771</v>
+        <v>14.064</v>
       </c>
       <c r="F49">
-        <v>13.771</v>
+        <v>14.064</v>
       </c>
       <c r="G49">
         <v>4.86</v>
@@ -5433,28 +5433,28 @@
         <v>5.061</v>
       </c>
       <c r="M49">
-        <v>0.7477653000000001</v>
+        <v>0.7636752000000001</v>
       </c>
       <c r="N49">
-        <v>4.3132347</v>
+        <v>4.2973248</v>
       </c>
       <c r="O49">
-        <v>1.078308675</v>
+        <v>1.0743312</v>
       </c>
       <c r="P49">
-        <v>3.234926025</v>
+        <v>3.2229936</v>
       </c>
       <c r="Q49">
-        <v>3.093926025</v>
+        <v>3.0819936</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2134615014412704</v>
+        <v>0.2162016654439061</v>
       </c>
       <c r="T49">
-        <v>1.025396871519516</v>
+        <v>1.042155373451084</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.768166428690926</v>
+        <v>6.627162961426532</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1319728660308312</v>
+        <v>0.131670386297789</v>
       </c>
       <c r="C50">
-        <v>19.35382781252083</v>
+        <v>19.16142319243491</v>
       </c>
       <c r="D50">
-        <v>28.55782781252083</v>
+        <v>28.65842319243491</v>
       </c>
       <c r="E50">
-        <v>14.064</v>
+        <v>14.357</v>
       </c>
       <c r="F50">
-        <v>14.064</v>
+        <v>14.357</v>
       </c>
       <c r="G50">
         <v>4.86</v>
@@ -5515,28 +5515,28 @@
         <v>5.061</v>
       </c>
       <c r="M50">
-        <v>0.7636752</v>
+        <v>0.7795851</v>
       </c>
       <c r="N50">
-        <v>4.2973248</v>
+        <v>4.2814149</v>
       </c>
       <c r="O50">
-        <v>1.0743312</v>
+        <v>1.070353725</v>
       </c>
       <c r="P50">
-        <v>3.2229936</v>
+        <v>3.211061175</v>
       </c>
       <c r="Q50">
-        <v>3.0819936</v>
+        <v>3.070061175</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2162016654439061</v>
+        <v>0.2190492868584099</v>
       </c>
       <c r="T50">
-        <v>1.042155373451084</v>
+        <v>1.059571071536831</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.627162961426533</v>
+        <v>6.49191473772395</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.131670386297789</v>
+        <v>0.1313679065647469</v>
       </c>
       <c r="C51">
-        <v>19.16142319243491</v>
+        <v>18.96972977506233</v>
       </c>
       <c r="D51">
-        <v>28.65842319243491</v>
+        <v>28.75972977506233</v>
       </c>
       <c r="E51">
-        <v>14.357</v>
+        <v>14.65</v>
       </c>
       <c r="F51">
-        <v>14.357</v>
+        <v>14.65</v>
       </c>
       <c r="G51">
         <v>4.86</v>
@@ -5597,28 +5597,28 @@
         <v>5.061</v>
       </c>
       <c r="M51">
-        <v>0.7795851</v>
+        <v>0.7954950000000001</v>
       </c>
       <c r="N51">
-        <v>4.2814149</v>
+        <v>4.265505</v>
       </c>
       <c r="O51">
-        <v>1.070353725</v>
+        <v>1.06637625</v>
       </c>
       <c r="P51">
-        <v>3.211061175</v>
+        <v>3.19912875</v>
       </c>
       <c r="Q51">
-        <v>3.070061175</v>
+        <v>3.05812875</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2190492868584099</v>
+        <v>0.2220108131294938</v>
       </c>
       <c r="T51">
-        <v>1.059571071536831</v>
+        <v>1.077683397546007</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.49191473772395</v>
+        <v>6.362076442969472</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1313679065647469</v>
+        <v>0.1310654268317047</v>
       </c>
       <c r="C52">
-        <v>18.96972977506233</v>
+        <v>18.77875512939375</v>
       </c>
       <c r="D52">
-        <v>28.75972977506233</v>
+        <v>28.86175512939375</v>
       </c>
       <c r="E52">
-        <v>14.65</v>
+        <v>14.943</v>
       </c>
       <c r="F52">
-        <v>14.65</v>
+        <v>14.943</v>
       </c>
       <c r="G52">
         <v>4.86</v>
@@ -5679,28 +5679,28 @@
         <v>5.061</v>
       </c>
       <c r="M52">
-        <v>0.7954950000000001</v>
+        <v>0.8114049000000001</v>
       </c>
       <c r="N52">
-        <v>4.265505</v>
+        <v>4.2495951</v>
       </c>
       <c r="O52">
-        <v>1.06637625</v>
+        <v>1.062398775</v>
       </c>
       <c r="P52">
-        <v>3.19912875</v>
+        <v>3.187196324999999</v>
       </c>
       <c r="Q52">
-        <v>3.05812875</v>
+        <v>3.046196324999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2220108131294938</v>
+        <v>0.2250932180238873</v>
       </c>
       <c r="T52">
-        <v>1.077683397546007</v>
+        <v>1.096535002167803</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.362076442969472</v>
+        <v>6.2373298460485</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1310654268317047</v>
+        <v>0.1307629470986626</v>
       </c>
       <c r="C53">
-        <v>18.77875512939375</v>
+        <v>18.58850693220643</v>
       </c>
       <c r="D53">
-        <v>28.86175512939375</v>
+        <v>28.96450693220643</v>
       </c>
       <c r="E53">
-        <v>14.943</v>
+        <v>15.236</v>
       </c>
       <c r="F53">
-        <v>14.943</v>
+        <v>15.236</v>
       </c>
       <c r="G53">
         <v>4.86</v>
@@ -5761,28 +5761,28 @@
         <v>5.061</v>
       </c>
       <c r="M53">
-        <v>0.8114049000000001</v>
+        <v>0.8273148</v>
       </c>
       <c r="N53">
-        <v>4.2495951</v>
+        <v>4.2336852</v>
       </c>
       <c r="O53">
-        <v>1.062398775</v>
+        <v>1.0584213</v>
       </c>
       <c r="P53">
-        <v>3.187196324999999</v>
+        <v>3.1752639</v>
       </c>
       <c r="Q53">
-        <v>3.046196324999999</v>
+        <v>3.0342639</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2250932180238873</v>
+        <v>0.2283040564555471</v>
       </c>
       <c r="T53">
-        <v>1.096535002167803</v>
+        <v>1.116172090315507</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.2373298460485</v>
+        <v>6.117381195162953</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1307629470986626</v>
+        <v>0.1308579673656205</v>
       </c>
       <c r="C54">
-        <v>18.58850693220643</v>
+        <v>18.26314999650432</v>
       </c>
       <c r="D54">
-        <v>28.96450693220643</v>
+        <v>28.93214999650433</v>
       </c>
       <c r="E54">
-        <v>15.236</v>
+        <v>15.529</v>
       </c>
       <c r="F54">
-        <v>15.236</v>
+        <v>15.529</v>
       </c>
       <c r="G54">
         <v>4.86</v>
@@ -5843,45 +5843,45 @@
         <v>5.061</v>
       </c>
       <c r="M54">
-        <v>0.8273148</v>
+        <v>0.8587537000000002</v>
       </c>
       <c r="N54">
-        <v>4.2336852</v>
+        <v>4.2022463</v>
       </c>
       <c r="O54">
-        <v>1.0584213</v>
+        <v>1.050561575</v>
       </c>
       <c r="P54">
-        <v>3.1752639</v>
+        <v>3.151684725</v>
       </c>
       <c r="Q54">
-        <v>3.0342639</v>
+        <v>3.010684725</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2283040564555471</v>
+        <v>0.2316515263098309</v>
       </c>
       <c r="T54">
-        <v>1.116172090315507</v>
+        <v>1.136644799235455</v>
       </c>
       <c r="U54">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V54">
         <v>0.25</v>
       </c>
       <c r="W54">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y54">
-        <v>6.117381195162953</v>
+        <v>5.893424389321407</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1308579673656205</v>
+        <v>0.1305629876325783</v>
       </c>
       <c r="C55">
-        <v>18.26314999650432</v>
+        <v>18.07083542679258</v>
       </c>
       <c r="D55">
-        <v>28.93214999650433</v>
+        <v>29.03283542679258</v>
       </c>
       <c r="E55">
-        <v>15.529</v>
+        <v>15.822</v>
       </c>
       <c r="F55">
-        <v>15.529</v>
+        <v>15.822</v>
       </c>
       <c r="G55">
         <v>4.86</v>
@@ -5925,28 +5925,28 @@
         <v>5.061</v>
       </c>
       <c r="M55">
-        <v>0.8587537000000002</v>
+        <v>0.8749566000000001</v>
       </c>
       <c r="N55">
-        <v>4.2022463</v>
+        <v>4.1860434</v>
       </c>
       <c r="O55">
-        <v>1.050561575</v>
+        <v>1.04651085</v>
       </c>
       <c r="P55">
-        <v>3.151684725</v>
+        <v>3.13953255</v>
       </c>
       <c r="Q55">
-        <v>3.010684725</v>
+        <v>2.99853255</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2316515263098309</v>
+        <v>0.2351445383316921</v>
       </c>
       <c r="T55">
-        <v>1.136644799235455</v>
+        <v>1.15800762593453</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.893424389321407</v>
+        <v>5.784286900630271</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1305629876325783</v>
+        <v>0.1302680078995362</v>
       </c>
       <c r="C56">
-        <v>18.07083542679258</v>
+        <v>17.87922408572529</v>
       </c>
       <c r="D56">
-        <v>29.03283542679258</v>
+        <v>29.13422408572529</v>
       </c>
       <c r="E56">
-        <v>15.822</v>
+        <v>16.115</v>
       </c>
       <c r="F56">
-        <v>15.822</v>
+        <v>16.115</v>
       </c>
       <c r="G56">
         <v>4.86</v>
@@ -6007,28 +6007,28 @@
         <v>5.061</v>
       </c>
       <c r="M56">
-        <v>0.8749566000000001</v>
+        <v>0.8911595000000001</v>
       </c>
       <c r="N56">
-        <v>4.1860434</v>
+        <v>4.169840499999999</v>
       </c>
       <c r="O56">
-        <v>1.04651085</v>
+        <v>1.042460125</v>
       </c>
       <c r="P56">
-        <v>3.13953255</v>
+        <v>3.127380375</v>
       </c>
       <c r="Q56">
-        <v>2.99853255</v>
+        <v>2.986380375</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2351445383316921</v>
+        <v>0.2387927953323027</v>
       </c>
       <c r="T56">
-        <v>1.15800762593453</v>
+        <v>1.180319911598008</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.784286900630271</v>
+        <v>5.679118047891538</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1302680078995362</v>
+        <v>0.1299730281664941</v>
       </c>
       <c r="C57">
-        <v>17.87922408572529</v>
+        <v>17.68832336658041</v>
       </c>
       <c r="D57">
-        <v>29.13422408572529</v>
+        <v>29.23632336658041</v>
       </c>
       <c r="E57">
-        <v>16.115</v>
+        <v>16.408</v>
       </c>
       <c r="F57">
-        <v>16.115</v>
+        <v>16.408</v>
       </c>
       <c r="G57">
         <v>4.86</v>
@@ -6089,28 +6089,28 @@
         <v>5.061</v>
       </c>
       <c r="M57">
-        <v>0.8911595000000001</v>
+        <v>0.9073624000000001</v>
       </c>
       <c r="N57">
-        <v>4.169840499999999</v>
+        <v>4.1536376</v>
       </c>
       <c r="O57">
-        <v>1.042460125</v>
+        <v>1.0384094</v>
       </c>
       <c r="P57">
-        <v>3.127380375</v>
+        <v>3.1152282</v>
       </c>
       <c r="Q57">
-        <v>2.986380375</v>
+        <v>2.9742282</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2387927953323027</v>
+        <v>0.2426068821965775</v>
       </c>
       <c r="T57">
-        <v>1.180319911598008</v>
+        <v>1.203646392064372</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.679118047891538</v>
+        <v>5.577705225607761</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1299730281664941</v>
+        <v>0.129678048433452</v>
       </c>
       <c r="C58">
-        <v>17.68832336658041</v>
+        <v>17.4981407666377</v>
       </c>
       <c r="D58">
-        <v>29.23632336658041</v>
+        <v>29.3391407666377</v>
       </c>
       <c r="E58">
-        <v>16.408</v>
+        <v>16.701</v>
       </c>
       <c r="F58">
-        <v>16.408</v>
+        <v>16.701</v>
       </c>
       <c r="G58">
         <v>4.86</v>
@@ -6171,28 +6171,28 @@
         <v>5.061</v>
       </c>
       <c r="M58">
-        <v>0.9073624000000001</v>
+        <v>0.9235653</v>
       </c>
       <c r="N58">
-        <v>4.1536376</v>
+        <v>4.1374347</v>
       </c>
       <c r="O58">
-        <v>1.0384094</v>
+        <v>1.034358675</v>
       </c>
       <c r="P58">
-        <v>3.1152282</v>
+        <v>3.103076025</v>
       </c>
       <c r="Q58">
-        <v>2.9742282</v>
+        <v>2.962076025</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2426068821965775</v>
+        <v>0.2465983684498883</v>
       </c>
       <c r="T58">
-        <v>1.203646392064372</v>
+        <v>1.228057825110566</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.577705225607761</v>
+        <v>5.47985074796552</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.129678048433452</v>
+        <v>0.1293830687004098</v>
       </c>
       <c r="C59">
-        <v>17.4981407666377</v>
+        <v>17.30868388901395</v>
       </c>
       <c r="D59">
-        <v>29.3391407666377</v>
+        <v>29.44268388901396</v>
       </c>
       <c r="E59">
-        <v>16.701</v>
+        <v>16.994</v>
       </c>
       <c r="F59">
-        <v>16.701</v>
+        <v>16.994</v>
       </c>
       <c r="G59">
         <v>4.86</v>
@@ -6253,28 +6253,28 @@
         <v>5.061</v>
       </c>
       <c r="M59">
-        <v>0.9235653</v>
+        <v>0.9397682000000002</v>
       </c>
       <c r="N59">
-        <v>4.1374347</v>
+        <v>4.121231799999999</v>
       </c>
       <c r="O59">
-        <v>1.034358675</v>
+        <v>1.03030795</v>
       </c>
       <c r="P59">
-        <v>3.103076025</v>
+        <v>3.090923849999999</v>
       </c>
       <c r="Q59">
-        <v>2.962076025</v>
+        <v>2.949923849999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2465983684498883</v>
+        <v>0.2507799254771663</v>
       </c>
       <c r="T59">
-        <v>1.228057825110566</v>
+        <v>1.253631707349437</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.47985074796552</v>
+        <v>5.385370562655768</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1293830687004098</v>
+        <v>0.1290880889673677</v>
       </c>
       <c r="C60">
-        <v>17.30868388901395</v>
+        <v>17.11996044453713</v>
       </c>
       <c r="D60">
-        <v>29.44268388901395</v>
+        <v>29.54696044453713</v>
       </c>
       <c r="E60">
-        <v>16.994</v>
+        <v>17.287</v>
       </c>
       <c r="F60">
-        <v>16.994</v>
+        <v>17.287</v>
       </c>
       <c r="G60">
         <v>4.86</v>
@@ -6335,28 +6335,28 @@
         <v>5.061</v>
       </c>
       <c r="M60">
-        <v>0.9397682000000001</v>
+        <v>0.9559711</v>
       </c>
       <c r="N60">
-        <v>4.1212318</v>
+        <v>4.1050289</v>
       </c>
       <c r="O60">
-        <v>1.03030795</v>
+        <v>1.026257225</v>
       </c>
       <c r="P60">
-        <v>3.09092385</v>
+        <v>3.078771675</v>
       </c>
       <c r="Q60">
-        <v>2.94992385</v>
+        <v>2.937771675</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2507799254771662</v>
+        <v>0.2551654608960187</v>
       </c>
       <c r="T60">
-        <v>1.253631707349437</v>
+        <v>1.280453096038984</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.38537056265577</v>
+        <v>5.294093095492112</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1290880889673677</v>
+        <v>0.1287931092343256</v>
       </c>
       <c r="C61">
-        <v>17.11996044453713</v>
+        <v>16.93197825366062</v>
       </c>
       <c r="D61">
-        <v>29.54696044453713</v>
+        <v>29.65197825366062</v>
       </c>
       <c r="E61">
-        <v>17.287</v>
+        <v>17.58</v>
       </c>
       <c r="F61">
-        <v>17.287</v>
+        <v>17.58</v>
       </c>
       <c r="G61">
         <v>4.86</v>
@@ -6417,28 +6417,28 @@
         <v>5.061</v>
       </c>
       <c r="M61">
-        <v>0.9559711</v>
+        <v>0.972174</v>
       </c>
       <c r="N61">
-        <v>4.1050289</v>
+        <v>4.088826</v>
       </c>
       <c r="O61">
-        <v>1.026257225</v>
+        <v>1.0222065</v>
       </c>
       <c r="P61">
-        <v>3.078771675</v>
+        <v>3.0666195</v>
       </c>
       <c r="Q61">
-        <v>2.937771675</v>
+        <v>2.9256195</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2551654608960187</v>
+        <v>0.2597702730858139</v>
       </c>
       <c r="T61">
-        <v>1.280453096038984</v>
+        <v>1.308615554163009</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.294093095492112</v>
+        <v>5.205858210567245</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1287931092343256</v>
+        <v>0.1284981295012834</v>
       </c>
       <c r="C62">
-        <v>16.93197825366062</v>
+        <v>16.74474524841834</v>
       </c>
       <c r="D62">
-        <v>29.65197825366062</v>
+        <v>29.75774524841834</v>
       </c>
       <c r="E62">
-        <v>17.58</v>
+        <v>17.873</v>
       </c>
       <c r="F62">
-        <v>17.58</v>
+        <v>17.873</v>
       </c>
       <c r="G62">
         <v>4.86</v>
@@ -6499,28 +6499,28 @@
         <v>5.061</v>
       </c>
       <c r="M62">
-        <v>0.972174</v>
+        <v>0.9883769000000001</v>
       </c>
       <c r="N62">
-        <v>4.088826</v>
+        <v>4.072623099999999</v>
       </c>
       <c r="O62">
-        <v>1.0222065</v>
+        <v>1.018155775</v>
       </c>
       <c r="P62">
-        <v>3.0666195</v>
+        <v>3.054467325</v>
       </c>
       <c r="Q62">
-        <v>2.9256195</v>
+        <v>2.913467325</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2597702730858139</v>
+        <v>0.2646112294904703</v>
       </c>
       <c r="T62">
-        <v>1.308615554163009</v>
+        <v>1.338222240908779</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.205858210567245</v>
+        <v>5.120516272689092</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1284981295012834</v>
+        <v>0.1282031497682413</v>
       </c>
       <c r="C63">
-        <v>16.74474524841834</v>
+        <v>16.55826947442187</v>
       </c>
       <c r="D63">
-        <v>29.75774524841834</v>
+        <v>29.86426947442187</v>
       </c>
       <c r="E63">
-        <v>17.873</v>
+        <v>18.166</v>
       </c>
       <c r="F63">
-        <v>17.873</v>
+        <v>18.166</v>
       </c>
       <c r="G63">
         <v>4.86</v>
@@ -6581,28 +6581,28 @@
         <v>5.061</v>
       </c>
       <c r="M63">
-        <v>0.9883769000000001</v>
+        <v>1.0045798</v>
       </c>
       <c r="N63">
-        <v>4.072623099999999</v>
+        <v>4.0564202</v>
       </c>
       <c r="O63">
-        <v>1.018155775</v>
+        <v>1.01410505</v>
       </c>
       <c r="P63">
-        <v>3.054467325</v>
+        <v>3.04231515</v>
       </c>
       <c r="Q63">
-        <v>2.913467325</v>
+        <v>2.90131515</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2646112294904703</v>
+        <v>0.2697069730743192</v>
       </c>
       <c r="T63">
-        <v>1.338222240908779</v>
+        <v>1.369387174325378</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.120516272689092</v>
+        <v>5.037927300548946</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1282031497682413</v>
+        <v>0.1279081700351992</v>
       </c>
       <c r="C64">
-        <v>16.55826947442187</v>
+        <v>16.37255909290061</v>
       </c>
       <c r="D64">
-        <v>29.86426947442187</v>
+        <v>29.9715590929006</v>
       </c>
       <c r="E64">
-        <v>18.166</v>
+        <v>18.459</v>
       </c>
       <c r="F64">
-        <v>18.166</v>
+        <v>18.459</v>
       </c>
       <c r="G64">
         <v>4.86</v>
@@ -6663,28 +6663,28 @@
         <v>5.061</v>
       </c>
       <c r="M64">
-        <v>1.0045798</v>
+        <v>1.0207827</v>
       </c>
       <c r="N64">
-        <v>4.0564202</v>
+        <v>4.0402173</v>
       </c>
       <c r="O64">
-        <v>1.01410505</v>
+        <v>1.010054325</v>
       </c>
       <c r="P64">
-        <v>3.04231515</v>
+        <v>3.030162975</v>
       </c>
       <c r="Q64">
-        <v>2.90131515</v>
+        <v>2.889162975</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2697069730743192</v>
+        <v>0.275078162257295</v>
       </c>
       <c r="T64">
-        <v>1.369387174325378</v>
+        <v>1.402236698737469</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.037927300548946</v>
+        <v>4.957960200540232</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1279081700351992</v>
+        <v>0.127613190302157</v>
       </c>
       <c r="C65">
-        <v>16.37255909290061</v>
+        <v>16.18762238278612</v>
       </c>
       <c r="D65">
-        <v>29.9715590929006</v>
+        <v>30.07962238278612</v>
       </c>
       <c r="E65">
-        <v>18.459</v>
+        <v>18.752</v>
       </c>
       <c r="F65">
-        <v>18.459</v>
+        <v>18.752</v>
       </c>
       <c r="G65">
         <v>4.86</v>
@@ -6745,28 +6745,28 @@
         <v>5.061</v>
       </c>
       <c r="M65">
-        <v>1.0207827</v>
+        <v>1.0369856</v>
       </c>
       <c r="N65">
-        <v>4.0402173</v>
+        <v>4.0240144</v>
       </c>
       <c r="O65">
-        <v>1.010054325</v>
+        <v>1.0060036</v>
       </c>
       <c r="P65">
-        <v>3.030162975</v>
+        <v>3.0180108</v>
       </c>
       <c r="Q65">
-        <v>2.889162975</v>
+        <v>2.8770108</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.275078162257295</v>
+        <v>0.2807477508393251</v>
       </c>
       <c r="T65">
-        <v>1.402236698737469</v>
+        <v>1.43691119672801</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.957960200540232</v>
+        <v>4.88049207240679</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.127613190302157</v>
+        <v>0.1273182105691149</v>
       </c>
       <c r="C66">
-        <v>16.18762238278612</v>
+        <v>16.0034677428417</v>
       </c>
       <c r="D66">
-        <v>30.07962238278612</v>
+        <v>30.1884677428417</v>
       </c>
       <c r="E66">
-        <v>18.752</v>
+        <v>19.045</v>
       </c>
       <c r="F66">
-        <v>18.752</v>
+        <v>19.045</v>
       </c>
       <c r="G66">
         <v>4.86</v>
@@ -6827,28 +6827,28 @@
         <v>5.061</v>
       </c>
       <c r="M66">
-        <v>1.0369856</v>
+        <v>1.0531885</v>
       </c>
       <c r="N66">
-        <v>4.0240144</v>
+        <v>4.0078115</v>
       </c>
       <c r="O66">
-        <v>1.0060036</v>
+        <v>1.001952875</v>
       </c>
       <c r="P66">
-        <v>3.0180108</v>
+        <v>3.005858625</v>
       </c>
       <c r="Q66">
-        <v>2.8770108</v>
+        <v>2.864858625</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2807477508393251</v>
+        <v>0.2867413159117568</v>
       </c>
       <c r="T66">
-        <v>1.43691119672801</v>
+        <v>1.473567094603724</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.88049207240679</v>
+        <v>4.805407578985148</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1273182105691149</v>
+        <v>0.1270232308360728</v>
       </c>
       <c r="C67">
-        <v>16.0034677428417</v>
+        <v>15.82010369383837</v>
       </c>
       <c r="D67">
-        <v>30.1884677428417</v>
+        <v>30.29810369383837</v>
       </c>
       <c r="E67">
-        <v>19.045</v>
+        <v>19.338</v>
       </c>
       <c r="F67">
-        <v>19.045</v>
+        <v>19.338</v>
       </c>
       <c r="G67">
         <v>4.86</v>
@@ -6909,28 +6909,28 @@
         <v>5.061</v>
       </c>
       <c r="M67">
-        <v>1.0531885</v>
+        <v>1.0693914</v>
       </c>
       <c r="N67">
-        <v>4.0078115</v>
+        <v>3.9916086</v>
       </c>
       <c r="O67">
-        <v>1.001952875</v>
+        <v>0.99790215</v>
       </c>
       <c r="P67">
-        <v>3.005858625</v>
+        <v>2.99370645</v>
       </c>
       <c r="Q67">
-        <v>2.864858625</v>
+        <v>2.85270645</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2867413159117568</v>
+        <v>0.2930874436355081</v>
       </c>
       <c r="T67">
-        <v>1.473567094603724</v>
+        <v>1.512379221766246</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.805407578985148</v>
+        <v>4.732598373242949</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1270232308360728</v>
+        <v>0.1267282511030306</v>
       </c>
       <c r="C68">
-        <v>15.82010369383837</v>
+        <v>15.63753888077839</v>
       </c>
       <c r="D68">
-        <v>30.29810369383837</v>
+        <v>30.40853888077838</v>
       </c>
       <c r="E68">
-        <v>19.338</v>
+        <v>19.631</v>
       </c>
       <c r="F68">
-        <v>19.338</v>
+        <v>19.631</v>
       </c>
       <c r="G68">
         <v>4.86</v>
@@ -6991,28 +6991,28 @@
         <v>5.061</v>
       </c>
       <c r="M68">
-        <v>1.0693914</v>
+        <v>1.0855943</v>
       </c>
       <c r="N68">
-        <v>3.9916086</v>
+        <v>3.9754057</v>
       </c>
       <c r="O68">
-        <v>0.99790215</v>
+        <v>0.9938514249999999</v>
       </c>
       <c r="P68">
-        <v>2.99370645</v>
+        <v>2.981554275</v>
       </c>
       <c r="Q68">
-        <v>2.85270645</v>
+        <v>2.840554275</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2930874436355081</v>
+        <v>0.2998181851606989</v>
       </c>
       <c r="T68">
-        <v>1.512379221766246</v>
+        <v>1.553543599059829</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.732598373242949</v>
+        <v>4.661962576627382</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1267282511030306</v>
+        <v>0.1264332713699885</v>
       </c>
       <c r="C69">
-        <v>15.63753888077839</v>
+        <v>15.45578207516763</v>
       </c>
       <c r="D69">
-        <v>30.40853888077838</v>
+        <v>30.51978207516763</v>
       </c>
       <c r="E69">
-        <v>19.631</v>
+        <v>19.924</v>
       </c>
       <c r="F69">
-        <v>19.631</v>
+        <v>19.924</v>
       </c>
       <c r="G69">
         <v>4.86</v>
@@ -7073,28 +7073,28 @@
         <v>5.061</v>
       </c>
       <c r="M69">
-        <v>1.0855943</v>
+        <v>1.1017972</v>
       </c>
       <c r="N69">
-        <v>3.9754057</v>
+        <v>3.9592028</v>
       </c>
       <c r="O69">
-        <v>0.9938514249999999</v>
+        <v>0.9898007</v>
       </c>
       <c r="P69">
-        <v>2.981554275</v>
+        <v>2.9694021</v>
       </c>
       <c r="Q69">
-        <v>2.840554275</v>
+        <v>2.8284021</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2998181851606989</v>
+        <v>0.3069695980312141</v>
       </c>
       <c r="T69">
-        <v>1.553543599059829</v>
+        <v>1.597280749934261</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.661962576627382</v>
+        <v>4.593404303441686</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1264332713699885</v>
+        <v>0.1261382916369463</v>
       </c>
       <c r="C70">
-        <v>15.45578207516763</v>
+        <v>15.2748421773381</v>
       </c>
       <c r="D70">
-        <v>30.51978207516763</v>
+        <v>30.63184217733811</v>
       </c>
       <c r="E70">
-        <v>19.924</v>
+        <v>20.217</v>
       </c>
       <c r="F70">
-        <v>19.924</v>
+        <v>20.217</v>
       </c>
       <c r="G70">
         <v>4.86</v>
@@ -7155,28 +7155,28 @@
         <v>5.061</v>
       </c>
       <c r="M70">
-        <v>1.1017972</v>
+        <v>1.1180001</v>
       </c>
       <c r="N70">
-        <v>3.9592028</v>
+        <v>3.9429999</v>
       </c>
       <c r="O70">
-        <v>0.9898007</v>
+        <v>0.9857499749999999</v>
       </c>
       <c r="P70">
-        <v>2.9694021</v>
+        <v>2.957249925</v>
       </c>
       <c r="Q70">
-        <v>2.8284021</v>
+        <v>2.816249925</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3069695980312141</v>
+        <v>0.3145823923772463</v>
       </c>
       <c r="T70">
-        <v>1.597280749934261</v>
+        <v>1.643839652478011</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.593404303441686</v>
+        <v>4.526833226580211</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1261382916369463</v>
+        <v>0.1271558119039042</v>
       </c>
       <c r="C71">
-        <v>15.2748421773381</v>
+        <v>14.59872854967852</v>
       </c>
       <c r="D71">
-        <v>30.63184217733811</v>
+        <v>30.24872854967851</v>
       </c>
       <c r="E71">
-        <v>20.217</v>
+        <v>20.51</v>
       </c>
       <c r="F71">
-        <v>20.217</v>
+        <v>20.51</v>
       </c>
       <c r="G71">
         <v>4.86</v>
@@ -7237,45 +7237,45 @@
         <v>5.061</v>
       </c>
       <c r="M71">
-        <v>1.1180001</v>
+        <v>1.185478</v>
       </c>
       <c r="N71">
-        <v>3.9429999</v>
+        <v>3.875522</v>
       </c>
       <c r="O71">
-        <v>0.9857499749999999</v>
+        <v>0.9688804999999999</v>
       </c>
       <c r="P71">
-        <v>2.957249925</v>
+        <v>2.9066415</v>
       </c>
       <c r="Q71">
-        <v>2.816249925</v>
+        <v>2.7656415</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3145823923772463</v>
+        <v>0.3227027063463475</v>
       </c>
       <c r="T71">
-        <v>1.643839652478011</v>
+        <v>1.693502481858012</v>
       </c>
       <c r="U71">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V71">
         <v>0.25</v>
       </c>
       <c r="W71">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y71">
-        <v>4.526833226580211</v>
+        <v>4.269163999669331</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1271558119039042</v>
+        <v>0.1268795821708621</v>
       </c>
       <c r="C72">
-        <v>14.59872854967852</v>
+        <v>14.40878283274737</v>
       </c>
       <c r="D72">
-        <v>30.24872854967851</v>
+        <v>30.35178283274738</v>
       </c>
       <c r="E72">
-        <v>20.51</v>
+        <v>20.803</v>
       </c>
       <c r="F72">
-        <v>20.51</v>
+        <v>20.803</v>
       </c>
       <c r="G72">
         <v>4.86</v>
@@ -7319,28 +7319,28 @@
         <v>5.061</v>
       </c>
       <c r="M72">
-        <v>1.185478</v>
+        <v>1.2024134</v>
       </c>
       <c r="N72">
-        <v>3.875522</v>
+        <v>3.8585866</v>
       </c>
       <c r="O72">
-        <v>0.9688804999999999</v>
+        <v>0.9646466499999999</v>
       </c>
       <c r="P72">
-        <v>2.9066415</v>
+        <v>2.89393995</v>
       </c>
       <c r="Q72">
-        <v>2.7656415</v>
+        <v>2.75293995</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3227027063463475</v>
+        <v>0.3313830419684901</v>
       </c>
       <c r="T72">
-        <v>1.693502481858012</v>
+        <v>1.746590333953874</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.269163999669331</v>
+        <v>4.209034929251453</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1268795821708621</v>
+        <v>0.1266033524378199</v>
       </c>
       <c r="C73">
-        <v>14.40878283274737</v>
+        <v>14.21954170680764</v>
       </c>
       <c r="D73">
-        <v>30.35178283274738</v>
+        <v>30.45554170680764</v>
       </c>
       <c r="E73">
-        <v>20.803</v>
+        <v>21.096</v>
       </c>
       <c r="F73">
-        <v>20.803</v>
+        <v>21.096</v>
       </c>
       <c r="G73">
         <v>4.86</v>
@@ -7401,28 +7401,28 @@
         <v>5.061</v>
       </c>
       <c r="M73">
-        <v>1.2024134</v>
+        <v>1.2193488</v>
       </c>
       <c r="N73">
-        <v>3.8585866</v>
+        <v>3.8416512</v>
       </c>
       <c r="O73">
-        <v>0.9646466499999999</v>
+        <v>0.9604128</v>
       </c>
       <c r="P73">
-        <v>2.89393995</v>
+        <v>2.8812384</v>
       </c>
       <c r="Q73">
-        <v>2.75293995</v>
+        <v>2.7402384</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3313830419684899</v>
+        <v>0.3406834015636427</v>
       </c>
       <c r="T73">
-        <v>1.746590333953874</v>
+        <v>1.803470175485155</v>
       </c>
       <c r="U73">
         <v>0.0578</v>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.209034929251454</v>
+        <v>4.150576110789627</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1266033524378199</v>
+        <v>0.1263271227047778</v>
       </c>
       <c r="C74">
-        <v>14.21954170680764</v>
+        <v>14.03101242267026</v>
       </c>
       <c r="D74">
-        <v>30.45554170680764</v>
+        <v>30.56001242267026</v>
       </c>
       <c r="E74">
-        <v>21.096</v>
+        <v>21.389</v>
       </c>
       <c r="F74">
-        <v>21.096</v>
+        <v>21.389</v>
       </c>
       <c r="G74">
         <v>4.86</v>
@@ -7483,28 +7483,28 @@
         <v>5.061</v>
       </c>
       <c r="M74">
-        <v>1.2193488</v>
+        <v>1.2362842</v>
       </c>
       <c r="N74">
-        <v>3.8416512</v>
+        <v>3.8247158</v>
       </c>
       <c r="O74">
-        <v>0.9604128</v>
+        <v>0.95617895</v>
       </c>
       <c r="P74">
-        <v>2.8812384</v>
+        <v>2.86853685</v>
       </c>
       <c r="Q74">
-        <v>2.7402384</v>
+        <v>2.72753685</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3406834015636427</v>
+        <v>0.3506726766843623</v>
       </c>
       <c r="T74">
-        <v>1.803470175485155</v>
+        <v>1.864563338611346</v>
       </c>
       <c r="U74">
         <v>0.0578</v>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.150576110789627</v>
+        <v>4.09371890379251</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1263271227047778</v>
+        <v>0.1260508929717357</v>
       </c>
       <c r="C75">
-        <v>14.03101242267026</v>
+        <v>13.8432023309776</v>
       </c>
       <c r="D75">
-        <v>30.56001242267026</v>
+        <v>30.6652023309776</v>
       </c>
       <c r="E75">
-        <v>21.389</v>
+        <v>21.682</v>
       </c>
       <c r="F75">
-        <v>21.389</v>
+        <v>21.682</v>
       </c>
       <c r="G75">
         <v>4.86</v>
@@ -7565,28 +7565,28 @@
         <v>5.061</v>
       </c>
       <c r="M75">
-        <v>1.2362842</v>
+        <v>1.2532196</v>
       </c>
       <c r="N75">
-        <v>3.8247158</v>
+        <v>3.8077804</v>
       </c>
       <c r="O75">
-        <v>0.95617895</v>
+        <v>0.9519451</v>
       </c>
       <c r="P75">
-        <v>2.86853685</v>
+        <v>2.8558353</v>
       </c>
       <c r="Q75">
-        <v>2.72753685</v>
+        <v>2.7148353</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3506726766843623</v>
+        <v>0.3614303575835988</v>
       </c>
       <c r="T75">
-        <v>1.864563338611346</v>
+        <v>1.930355975824167</v>
       </c>
       <c r="U75">
         <v>0.0578</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.09371890379251</v>
+        <v>4.038398378065584</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1260508929717357</v>
+        <v>0.1277434132386936</v>
       </c>
       <c r="C76">
-        <v>13.8432023309776</v>
+        <v>12.91682041064728</v>
       </c>
       <c r="D76">
-        <v>30.6652023309776</v>
+        <v>30.03182041064728</v>
       </c>
       <c r="E76">
-        <v>21.682</v>
+        <v>21.975</v>
       </c>
       <c r="F76">
-        <v>21.682</v>
+        <v>21.975</v>
       </c>
       <c r="G76">
         <v>4.86</v>
@@ -7647,45 +7647,45 @@
         <v>5.061</v>
       </c>
       <c r="M76">
-        <v>1.2532196</v>
+        <v>1.3470675</v>
       </c>
       <c r="N76">
-        <v>3.8077804</v>
+        <v>3.7139325</v>
       </c>
       <c r="O76">
-        <v>0.9519451</v>
+        <v>0.928483125</v>
       </c>
       <c r="P76">
-        <v>2.8558353</v>
+        <v>2.785449375</v>
       </c>
       <c r="Q76">
-        <v>2.7148353</v>
+        <v>2.644449375</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3614303575835988</v>
+        <v>0.3730486529547742</v>
       </c>
       <c r="T76">
-        <v>1.930355975824167</v>
+        <v>2.001412024014014</v>
       </c>
       <c r="U76">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V76">
         <v>0.25</v>
       </c>
       <c r="W76">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y76">
-        <v>4.038398378065584</v>
+        <v>3.757050036468105</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1277434132386936</v>
+        <v>0.1274934335056514</v>
       </c>
       <c r="C77">
-        <v>12.91682041064728</v>
+        <v>12.71571698209576</v>
       </c>
       <c r="D77">
-        <v>30.03182041064728</v>
+        <v>30.12371698209576</v>
       </c>
       <c r="E77">
-        <v>21.975</v>
+        <v>22.268</v>
       </c>
       <c r="F77">
-        <v>21.975</v>
+        <v>22.268</v>
       </c>
       <c r="G77">
         <v>4.86</v>
@@ -7729,28 +7729,28 @@
         <v>5.061</v>
       </c>
       <c r="M77">
-        <v>1.3470675</v>
+        <v>1.3650284</v>
       </c>
       <c r="N77">
-        <v>3.7139325</v>
+        <v>3.6959716</v>
       </c>
       <c r="O77">
-        <v>0.928483125</v>
+        <v>0.9239929</v>
       </c>
       <c r="P77">
-        <v>2.785449375</v>
+        <v>2.7719787</v>
       </c>
       <c r="Q77">
-        <v>2.644449375</v>
+        <v>2.6309787</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3730486529547742</v>
+        <v>0.385635139606881</v>
       </c>
       <c r="T77">
-        <v>2.001412024014014</v>
+        <v>2.078389409553014</v>
       </c>
       <c r="U77">
         <v>0.0613</v>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.757050036468105</v>
+        <v>3.70761516756721</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1274934335056514</v>
+        <v>0.1272434537726093</v>
       </c>
       <c r="C78">
-        <v>12.71571698209576</v>
+        <v>12.51517768188933</v>
       </c>
       <c r="D78">
-        <v>30.12371698209576</v>
+        <v>30.21617768188933</v>
       </c>
       <c r="E78">
-        <v>22.268</v>
+        <v>22.561</v>
       </c>
       <c r="F78">
-        <v>22.268</v>
+        <v>22.561</v>
       </c>
       <c r="G78">
         <v>4.86</v>
@@ -7811,28 +7811,28 @@
         <v>5.061</v>
       </c>
       <c r="M78">
-        <v>1.3650284</v>
+        <v>1.3829893</v>
       </c>
       <c r="N78">
-        <v>3.6959716</v>
+        <v>3.6780107</v>
       </c>
       <c r="O78">
-        <v>0.9239929</v>
+        <v>0.9195026749999999</v>
       </c>
       <c r="P78">
-        <v>2.7719787</v>
+        <v>2.758508025</v>
       </c>
       <c r="Q78">
-        <v>2.6309787</v>
+        <v>2.617508025</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.385635139606881</v>
+        <v>0.3993161033591708</v>
       </c>
       <c r="T78">
-        <v>2.078389409553014</v>
+        <v>2.162060480791058</v>
       </c>
       <c r="U78">
         <v>0.0613</v>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.70761516756721</v>
+        <v>3.659464321235168</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1272434537726093</v>
+        <v>0.1269934740395671</v>
       </c>
       <c r="C79">
-        <v>12.51517768188933</v>
+        <v>12.31520772056944</v>
       </c>
       <c r="D79">
-        <v>30.21617768188933</v>
+        <v>30.30920772056944</v>
       </c>
       <c r="E79">
-        <v>22.561</v>
+        <v>22.854</v>
       </c>
       <c r="F79">
-        <v>22.561</v>
+        <v>22.854</v>
       </c>
       <c r="G79">
         <v>4.86</v>
@@ -7893,28 +7893,28 @@
         <v>5.061</v>
       </c>
       <c r="M79">
-        <v>1.3829893</v>
+        <v>1.4009502</v>
       </c>
       <c r="N79">
-        <v>3.6780107</v>
+        <v>3.660049799999999</v>
       </c>
       <c r="O79">
-        <v>0.9195026749999999</v>
+        <v>0.9150124499999999</v>
       </c>
       <c r="P79">
-        <v>2.758508025</v>
+        <v>2.74503735</v>
       </c>
       <c r="Q79">
-        <v>2.617508025</v>
+        <v>2.60403735</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3993161033591708</v>
+        <v>0.4142407910889416</v>
       </c>
       <c r="T79">
-        <v>2.162060480791058</v>
+        <v>2.253338013050743</v>
       </c>
       <c r="U79">
         <v>0.0613</v>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.659464321235168</v>
+        <v>3.612548111988562</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1269934740395671</v>
+        <v>0.126743494306525</v>
       </c>
       <c r="C80">
-        <v>12.31520772056944</v>
+        <v>12.11581237304482</v>
       </c>
       <c r="D80">
-        <v>30.30920772056944</v>
+        <v>30.40281237304482</v>
       </c>
       <c r="E80">
-        <v>22.854</v>
+        <v>23.147</v>
       </c>
       <c r="F80">
-        <v>22.854</v>
+        <v>23.147</v>
       </c>
       <c r="G80">
         <v>4.86</v>
@@ -7975,28 +7975,28 @@
         <v>5.061</v>
       </c>
       <c r="M80">
-        <v>1.4009502</v>
+        <v>1.4189111</v>
       </c>
       <c r="N80">
-        <v>3.660049799999999</v>
+        <v>3.6420889</v>
       </c>
       <c r="O80">
-        <v>0.9150124499999999</v>
+        <v>0.910522225</v>
       </c>
       <c r="P80">
-        <v>2.74503735</v>
+        <v>2.731566675</v>
       </c>
       <c r="Q80">
-        <v>2.60403735</v>
+        <v>2.590566675</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4142407910889416</v>
+        <v>0.4305868776501192</v>
       </c>
       <c r="T80">
-        <v>2.253338013050743</v>
+        <v>2.353308643620873</v>
       </c>
       <c r="U80">
         <v>0.0613</v>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.612548111988562</v>
+        <v>3.566819654874784</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.126743494306525</v>
+        <v>0.1264935145734829</v>
       </c>
       <c r="C81">
-        <v>12.11581237304482</v>
+        <v>11.91699697958868</v>
       </c>
       <c r="D81">
-        <v>30.40281237304482</v>
+        <v>30.49699697958868</v>
       </c>
       <c r="E81">
-        <v>23.147</v>
+        <v>23.44</v>
       </c>
       <c r="F81">
-        <v>23.147</v>
+        <v>23.44</v>
       </c>
       <c r="G81">
         <v>4.86</v>
@@ -8057,28 +8057,28 @@
         <v>5.061</v>
       </c>
       <c r="M81">
-        <v>1.4189111</v>
+        <v>1.436872</v>
       </c>
       <c r="N81">
-        <v>3.6420889</v>
+        <v>3.624128</v>
       </c>
       <c r="O81">
-        <v>0.910522225</v>
+        <v>0.9060319999999999</v>
       </c>
       <c r="P81">
-        <v>2.731566675</v>
+        <v>2.718096</v>
       </c>
       <c r="Q81">
-        <v>2.590566675</v>
+        <v>2.577096</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4305868776501192</v>
+        <v>0.4485675728674144</v>
       </c>
       <c r="T81">
-        <v>2.353308643620873</v>
+        <v>2.463276337248017</v>
       </c>
       <c r="U81">
         <v>0.0613</v>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.566819654874784</v>
+        <v>3.522234409188849</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1264935145734829</v>
+        <v>0.1279445348404408</v>
       </c>
       <c r="C82">
-        <v>11.91699697958868</v>
+        <v>11.08529089543235</v>
       </c>
       <c r="D82">
-        <v>30.49699697958868</v>
+        <v>29.95829089543235</v>
       </c>
       <c r="E82">
-        <v>23.44</v>
+        <v>23.733</v>
       </c>
       <c r="F82">
-        <v>23.44</v>
+        <v>23.733</v>
       </c>
       <c r="G82">
         <v>4.86</v>
@@ -8139,45 +8139,45 @@
         <v>5.061</v>
       </c>
       <c r="M82">
-        <v>1.436872</v>
+        <v>1.5212853</v>
       </c>
       <c r="N82">
-        <v>3.624128</v>
+        <v>3.5397147</v>
       </c>
       <c r="O82">
-        <v>0.9060319999999999</v>
+        <v>0.8849286749999999</v>
       </c>
       <c r="P82">
-        <v>2.718096</v>
+        <v>2.654786025</v>
       </c>
       <c r="Q82">
-        <v>2.577096</v>
+        <v>2.513786025</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4485675728674144</v>
+        <v>0.4684409728444251</v>
       </c>
       <c r="T82">
-        <v>2.463276337248017</v>
+        <v>2.584819577572755</v>
       </c>
       <c r="U82">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V82">
         <v>0.25</v>
       </c>
       <c r="W82">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y82">
-        <v>3.522234409188849</v>
+        <v>3.32679215397664</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1279445348404408</v>
+        <v>0.1277155551073986</v>
       </c>
       <c r="C83">
-        <v>11.08529089543235</v>
+        <v>10.87603373820063</v>
       </c>
       <c r="D83">
-        <v>29.95829089543235</v>
+        <v>30.04203373820063</v>
       </c>
       <c r="E83">
-        <v>23.733</v>
+        <v>24.026</v>
       </c>
       <c r="F83">
-        <v>23.733</v>
+        <v>24.026</v>
       </c>
       <c r="G83">
         <v>4.86</v>
@@ -8221,28 +8221,28 @@
         <v>5.061</v>
       </c>
       <c r="M83">
-        <v>1.5212853</v>
+        <v>1.5400666</v>
       </c>
       <c r="N83">
-        <v>3.5397147</v>
+        <v>3.5209334</v>
       </c>
       <c r="O83">
-        <v>0.8849286749999999</v>
+        <v>0.8802333499999999</v>
       </c>
       <c r="P83">
-        <v>2.654786025</v>
+        <v>2.64070005</v>
       </c>
       <c r="Q83">
-        <v>2.513786025</v>
+        <v>2.49970005</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4684409728444251</v>
+        <v>0.4905225283744369</v>
       </c>
       <c r="T83">
-        <v>2.584819577572755</v>
+        <v>2.719867622378019</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.32679215397664</v>
+        <v>3.286221517952534</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1277155551073986</v>
+        <v>0.1274865753743565</v>
       </c>
       <c r="C84">
-        <v>10.87603373820063</v>
+        <v>10.66724606848734</v>
       </c>
       <c r="D84">
-        <v>30.04203373820063</v>
+        <v>30.12624606848734</v>
       </c>
       <c r="E84">
-        <v>24.026</v>
+        <v>24.319</v>
       </c>
       <c r="F84">
-        <v>24.026</v>
+        <v>24.319</v>
       </c>
       <c r="G84">
         <v>4.86</v>
@@ -8303,28 +8303,28 @@
         <v>5.061</v>
       </c>
       <c r="M84">
-        <v>1.5400666</v>
+        <v>1.5588479</v>
       </c>
       <c r="N84">
-        <v>3.5209334</v>
+        <v>3.5021521</v>
       </c>
       <c r="O84">
-        <v>0.8802333499999999</v>
+        <v>0.875538025</v>
       </c>
       <c r="P84">
-        <v>2.64070005</v>
+        <v>2.626614075</v>
       </c>
       <c r="Q84">
-        <v>2.49970005</v>
+        <v>2.485614075</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4905225283744369</v>
+        <v>0.5152019139668029</v>
       </c>
       <c r="T84">
-        <v>2.719867622378019</v>
+        <v>2.870803672454491</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.286221517952534</v>
+        <v>3.246628487615757</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1274865753743565</v>
+        <v>0.1272575956413143</v>
       </c>
       <c r="C85">
-        <v>10.66724606848734</v>
+        <v>10.4589318455228</v>
       </c>
       <c r="D85">
-        <v>30.12624606848734</v>
+        <v>30.2109318455228</v>
       </c>
       <c r="E85">
-        <v>24.319</v>
+        <v>24.612</v>
       </c>
       <c r="F85">
-        <v>24.319</v>
+        <v>24.612</v>
       </c>
       <c r="G85">
         <v>4.86</v>
@@ -8385,28 +8385,28 @@
         <v>5.061</v>
       </c>
       <c r="M85">
-        <v>1.5588479</v>
+        <v>1.5776292</v>
       </c>
       <c r="N85">
-        <v>3.5021521</v>
+        <v>3.483370799999999</v>
       </c>
       <c r="O85">
-        <v>0.875538025</v>
+        <v>0.8708426999999999</v>
       </c>
       <c r="P85">
-        <v>2.626614075</v>
+        <v>2.6125281</v>
       </c>
       <c r="Q85">
-        <v>2.485614075</v>
+        <v>2.4715281</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5152019139668029</v>
+        <v>0.5429662227582148</v>
       </c>
       <c r="T85">
-        <v>2.870803672454491</v>
+        <v>3.040606728790522</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.246628487615757</v>
+        <v>3.207978148477474</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1272575956413143</v>
+        <v>0.1270286159082722</v>
       </c>
       <c r="C86">
-        <v>10.4589318455228</v>
+        <v>10.25109507318081</v>
       </c>
       <c r="D86">
-        <v>30.2109318455228</v>
+        <v>30.29609507318081</v>
       </c>
       <c r="E86">
-        <v>24.612</v>
+        <v>24.905</v>
       </c>
       <c r="F86">
-        <v>24.612</v>
+        <v>24.905</v>
       </c>
       <c r="G86">
         <v>4.86</v>
@@ -8467,28 +8467,28 @@
         <v>5.061</v>
       </c>
       <c r="M86">
-        <v>1.5776292</v>
+        <v>1.5964105</v>
       </c>
       <c r="N86">
-        <v>3.4833708</v>
+        <v>3.4645895</v>
       </c>
       <c r="O86">
-        <v>0.8708427</v>
+        <v>0.8661473749999999</v>
       </c>
       <c r="P86">
-        <v>2.6125281</v>
+        <v>2.598442125</v>
       </c>
       <c r="Q86">
-        <v>2.4715281</v>
+        <v>2.457442125</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5429662227582145</v>
+        <v>0.5744324393884813</v>
       </c>
       <c r="T86">
-        <v>3.04060672879052</v>
+        <v>3.233050192638022</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.207978148477475</v>
+        <v>3.170237229083622</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1270286159082722</v>
+        <v>0.1267996361752301</v>
       </c>
       <c r="C87">
-        <v>10.25109507318081</v>
+        <v>10.04373980060981</v>
       </c>
       <c r="D87">
-        <v>30.29609507318081</v>
+        <v>30.38173980060981</v>
       </c>
       <c r="E87">
-        <v>24.905</v>
+        <v>25.198</v>
       </c>
       <c r="F87">
-        <v>24.905</v>
+        <v>25.198</v>
       </c>
       <c r="G87">
         <v>4.86</v>
@@ -8549,28 +8549,28 @@
         <v>5.061</v>
       </c>
       <c r="M87">
-        <v>1.5964105</v>
+        <v>1.6151918</v>
       </c>
       <c r="N87">
-        <v>3.4645895</v>
+        <v>3.4458082</v>
       </c>
       <c r="O87">
-        <v>0.8661473749999999</v>
+        <v>0.86145205</v>
       </c>
       <c r="P87">
-        <v>2.598442125</v>
+        <v>2.58435615</v>
       </c>
       <c r="Q87">
-        <v>2.457442125</v>
+        <v>2.44335615</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5744324393884813</v>
+        <v>0.6103938298230719</v>
       </c>
       <c r="T87">
-        <v>3.233050192638022</v>
+        <v>3.452985579892309</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.170237229083622</v>
+        <v>3.133374005489627</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1267996361752301</v>
+        <v>0.126570656442188</v>
       </c>
       <c r="C88">
-        <v>10.04373980060981</v>
+        <v>9.836870122874537</v>
       </c>
       <c r="D88">
-        <v>30.38173980060981</v>
+        <v>30.46787012287454</v>
       </c>
       <c r="E88">
-        <v>25.198</v>
+        <v>25.491</v>
       </c>
       <c r="F88">
-        <v>25.198</v>
+        <v>25.491</v>
       </c>
       <c r="G88">
         <v>4.86</v>
@@ -8631,28 +8631,28 @@
         <v>5.061</v>
       </c>
       <c r="M88">
-        <v>1.6151918</v>
+        <v>1.6339731</v>
       </c>
       <c r="N88">
-        <v>3.4458082</v>
+        <v>3.4270269</v>
       </c>
       <c r="O88">
-        <v>0.86145205</v>
+        <v>0.8567567249999999</v>
       </c>
       <c r="P88">
-        <v>2.58435615</v>
+        <v>2.570270175</v>
       </c>
       <c r="Q88">
-        <v>2.44335615</v>
+        <v>2.429270175</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6103938298230719</v>
+        <v>0.651887741862984</v>
       </c>
       <c r="T88">
-        <v>3.452985579892309</v>
+        <v>3.706757180570332</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.133374005489627</v>
+        <v>3.097358212323079</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.126570656442188</v>
+        <v>0.1263416767091458</v>
       </c>
       <c r="C89">
-        <v>9.836870122874537</v>
+        <v>9.630490181608753</v>
       </c>
       <c r="D89">
-        <v>30.46787012287454</v>
+        <v>30.55449018160876</v>
       </c>
       <c r="E89">
-        <v>25.491</v>
+        <v>25.784</v>
       </c>
       <c r="F89">
-        <v>25.491</v>
+        <v>25.784</v>
       </c>
       <c r="G89">
         <v>4.86</v>
@@ -8713,28 +8713,28 @@
         <v>5.061</v>
       </c>
       <c r="M89">
-        <v>1.6339731</v>
+        <v>1.6527544</v>
       </c>
       <c r="N89">
-        <v>3.4270269</v>
+        <v>3.4082456</v>
       </c>
       <c r="O89">
-        <v>0.8567567249999999</v>
+        <v>0.8520614</v>
       </c>
       <c r="P89">
-        <v>2.570270175</v>
+        <v>2.5561842</v>
       </c>
       <c r="Q89">
-        <v>2.429270175</v>
+        <v>2.4151842</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.651887741862984</v>
+        <v>0.7002973059095484</v>
       </c>
       <c r="T89">
-        <v>3.706757180570332</v>
+        <v>4.002824048028027</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.097358212323079</v>
+        <v>3.062160959910317</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1263416767091458</v>
+        <v>0.1261126969761037</v>
       </c>
       <c r="C90">
-        <v>9.630490181608753</v>
+        <v>9.42460416567911</v>
       </c>
       <c r="D90">
-        <v>30.55449018160876</v>
+        <v>30.64160416567911</v>
       </c>
       <c r="E90">
-        <v>25.784</v>
+        <v>26.077</v>
       </c>
       <c r="F90">
-        <v>25.784</v>
+        <v>26.077</v>
       </c>
       <c r="G90">
         <v>4.86</v>
@@ -8795,28 +8795,28 @@
         <v>5.061</v>
       </c>
       <c r="M90">
-        <v>1.6527544</v>
+        <v>1.6715357</v>
       </c>
       <c r="N90">
-        <v>3.4082456</v>
+        <v>3.3894643</v>
       </c>
       <c r="O90">
-        <v>0.8520614</v>
+        <v>0.8473660749999999</v>
       </c>
       <c r="P90">
-        <v>2.5561842</v>
+        <v>2.542098225</v>
       </c>
       <c r="Q90">
-        <v>2.4151842</v>
+        <v>2.401098225</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7002973059095484</v>
+        <v>0.7575086088736697</v>
       </c>
       <c r="T90">
-        <v>4.002824048028027</v>
+        <v>4.352721255023484</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.062160959910317</v>
+        <v>3.027754656989976</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1261126969761037</v>
+        <v>0.1311487172430615</v>
       </c>
       <c r="C91">
-        <v>9.42460416567911</v>
+        <v>7.323589416599741</v>
       </c>
       <c r="D91">
-        <v>30.64160416567911</v>
+        <v>28.83358941659974</v>
       </c>
       <c r="E91">
-        <v>26.077</v>
+        <v>26.37</v>
       </c>
       <c r="F91">
-        <v>26.077</v>
+        <v>26.37</v>
       </c>
       <c r="G91">
         <v>4.86</v>
@@ -8877,45 +8877,45 @@
         <v>5.061</v>
       </c>
       <c r="M91">
-        <v>1.6715357</v>
+        <v>1.896003</v>
       </c>
       <c r="N91">
-        <v>3.3894643</v>
+        <v>3.164997</v>
       </c>
       <c r="O91">
-        <v>0.8473660749999999</v>
+        <v>0.7912492499999999</v>
       </c>
       <c r="P91">
-        <v>2.542098225</v>
+        <v>2.37374775</v>
       </c>
       <c r="Q91">
-        <v>2.401098225</v>
+        <v>2.23274775</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7575086088736697</v>
+        <v>0.8261621724306154</v>
       </c>
       <c r="T91">
-        <v>4.352721255023484</v>
+        <v>4.772597903418033</v>
       </c>
       <c r="U91">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V91">
         <v>0.25</v>
       </c>
       <c r="W91">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y91">
-        <v>3.027754656989976</v>
+        <v>2.669299573893078</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1311487172430615</v>
+        <v>0.1309782375100194</v>
       </c>
       <c r="C92">
-        <v>7.323589416599741</v>
+        <v>7.088298319367414</v>
       </c>
       <c r="D92">
-        <v>28.83358941659974</v>
+        <v>28.89129831936742</v>
       </c>
       <c r="E92">
-        <v>26.37</v>
+        <v>26.663</v>
       </c>
       <c r="F92">
-        <v>26.37</v>
+        <v>26.663</v>
       </c>
       <c r="G92">
         <v>4.86</v>
@@ -8959,28 +8959,28 @@
         <v>5.061</v>
       </c>
       <c r="M92">
-        <v>1.896003</v>
+        <v>1.9170697</v>
       </c>
       <c r="N92">
-        <v>3.164997</v>
+        <v>3.1439303</v>
       </c>
       <c r="O92">
-        <v>0.7912492499999999</v>
+        <v>0.785982575</v>
       </c>
       <c r="P92">
-        <v>2.37374775</v>
+        <v>2.357947725</v>
       </c>
       <c r="Q92">
-        <v>2.23274775</v>
+        <v>2.216947725</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8261621724306154</v>
+        <v>0.9100720834446603</v>
       </c>
       <c r="T92">
-        <v>4.772597903418033</v>
+        <v>5.285780473678037</v>
       </c>
       <c r="U92">
         <v>0.07190000000000001</v>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.669299573893078</v>
+        <v>2.639966611542606</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1309782375100194</v>
+        <v>0.1308077577769773</v>
       </c>
       <c r="C93">
-        <v>7.088298319367414</v>
+        <v>6.853238688029386</v>
       </c>
       <c r="D93">
-        <v>28.89129831936742</v>
+        <v>28.94923868802939</v>
       </c>
       <c r="E93">
-        <v>26.663</v>
+        <v>26.956</v>
       </c>
       <c r="F93">
-        <v>26.663</v>
+        <v>26.956</v>
       </c>
       <c r="G93">
         <v>4.86</v>
@@ -9041,28 +9041,28 @@
         <v>5.061</v>
       </c>
       <c r="M93">
-        <v>1.9170697</v>
+        <v>1.9381364</v>
       </c>
       <c r="N93">
-        <v>3.1439303</v>
+        <v>3.1228636</v>
       </c>
       <c r="O93">
-        <v>0.785982575</v>
+        <v>0.7807158999999999</v>
       </c>
       <c r="P93">
-        <v>2.357947725</v>
+        <v>2.3421477</v>
       </c>
       <c r="Q93">
-        <v>2.216947725</v>
+        <v>2.2011477</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9100720834446603</v>
+        <v>1.014959472212216</v>
       </c>
       <c r="T93">
-        <v>5.285780473678037</v>
+        <v>5.927258686503043</v>
       </c>
       <c r="U93">
         <v>0.07190000000000001</v>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.639966611542606</v>
+        <v>2.611271322286707</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1308077577769773</v>
+        <v>0.1306372780439351</v>
       </c>
       <c r="C94">
-        <v>6.853238688029386</v>
+        <v>6.618411917971457</v>
       </c>
       <c r="D94">
-        <v>28.94923868802939</v>
+        <v>29.00741191797146</v>
       </c>
       <c r="E94">
-        <v>26.956</v>
+        <v>27.249</v>
       </c>
       <c r="F94">
-        <v>26.956</v>
+        <v>27.249</v>
       </c>
       <c r="G94">
         <v>4.86</v>
@@ -9123,28 +9123,28 @@
         <v>5.061</v>
       </c>
       <c r="M94">
-        <v>1.9381364</v>
+        <v>1.9592031</v>
       </c>
       <c r="N94">
-        <v>3.1228636</v>
+        <v>3.1017969</v>
       </c>
       <c r="O94">
-        <v>0.7807158999999999</v>
+        <v>0.7754492249999999</v>
       </c>
       <c r="P94">
-        <v>2.3421477</v>
+        <v>2.326347675</v>
       </c>
       <c r="Q94">
-        <v>2.2011477</v>
+        <v>2.185347675</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.014959472212216</v>
+        <v>1.149814686341931</v>
       </c>
       <c r="T94">
-        <v>5.927258686503043</v>
+        <v>6.752016388706622</v>
       </c>
       <c r="U94">
         <v>0.07190000000000001</v>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.611271322286707</v>
+        <v>2.58319313602556</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1306372780439351</v>
+        <v>0.130466798310893</v>
       </c>
       <c r="C95">
-        <v>6.618411917971457</v>
+        <v>6.383819415818024</v>
       </c>
       <c r="D95">
-        <v>29.00741191797146</v>
+        <v>29.06581941581802</v>
       </c>
       <c r="E95">
-        <v>27.249</v>
+        <v>27.542</v>
       </c>
       <c r="F95">
-        <v>27.249</v>
+        <v>27.542</v>
       </c>
       <c r="G95">
         <v>4.86</v>
@@ -9205,28 +9205,28 @@
         <v>5.061</v>
       </c>
       <c r="M95">
-        <v>1.9592031</v>
+        <v>1.9802698</v>
       </c>
       <c r="N95">
-        <v>3.1017969</v>
+        <v>3.0807302</v>
       </c>
       <c r="O95">
-        <v>0.7754492249999999</v>
+        <v>0.7701825499999999</v>
       </c>
       <c r="P95">
-        <v>2.326347675</v>
+        <v>2.31054765</v>
       </c>
       <c r="Q95">
-        <v>2.185347675</v>
+        <v>2.16954765</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.149814686341931</v>
+        <v>1.329621638514884</v>
       </c>
       <c r="T95">
-        <v>6.752016388706622</v>
+        <v>7.85169332497806</v>
       </c>
       <c r="U95">
         <v>0.07190000000000001</v>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.58319313602556</v>
+        <v>2.555712357982735</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.130466798310893</v>
+        <v>0.1302963185778509</v>
       </c>
       <c r="C96">
-        <v>6.383819415818024</v>
+        <v>6.149462599545537</v>
       </c>
       <c r="D96">
-        <v>29.06581941581802</v>
+        <v>29.12446259954553</v>
       </c>
       <c r="E96">
-        <v>27.542</v>
+        <v>27.835</v>
       </c>
       <c r="F96">
-        <v>27.542</v>
+        <v>27.835</v>
       </c>
       <c r="G96">
         <v>4.86</v>
@@ -9287,28 +9287,28 @@
         <v>5.061</v>
       </c>
       <c r="M96">
-        <v>1.9802698</v>
+        <v>2.0013365</v>
       </c>
       <c r="N96">
-        <v>3.0807302</v>
+        <v>3.0596635</v>
       </c>
       <c r="O96">
-        <v>0.7701825499999999</v>
+        <v>0.7649158749999999</v>
       </c>
       <c r="P96">
-        <v>2.31054765</v>
+        <v>2.294747625</v>
       </c>
       <c r="Q96">
-        <v>2.16954765</v>
+        <v>2.153747625</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.329621638514884</v>
+        <v>1.58135137155702</v>
       </c>
       <c r="T96">
-        <v>7.85169332497806</v>
+        <v>9.391241035758076</v>
       </c>
       <c r="U96">
         <v>0.07190000000000001</v>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.555712357982735</v>
+        <v>2.528810122635548</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1302963185778509</v>
+        <v>0.1301258388448087</v>
       </c>
       <c r="C97">
-        <v>6.149462599545537</v>
+        <v>5.915342898597213</v>
       </c>
       <c r="D97">
-        <v>29.12446259954553</v>
+        <v>29.18334289859721</v>
       </c>
       <c r="E97">
-        <v>27.835</v>
+        <v>28.128</v>
       </c>
       <c r="F97">
-        <v>27.835</v>
+        <v>28.128</v>
       </c>
       <c r="G97">
         <v>4.86</v>
@@ -9369,28 +9369,28 @@
         <v>5.061</v>
       </c>
       <c r="M97">
-        <v>2.0013365</v>
+        <v>2.0224032</v>
       </c>
       <c r="N97">
-        <v>3.0596635</v>
+        <v>3.0385968</v>
       </c>
       <c r="O97">
-        <v>0.7649158749999999</v>
+        <v>0.7596491999999999</v>
       </c>
       <c r="P97">
-        <v>2.294747625</v>
+        <v>2.2789476</v>
       </c>
       <c r="Q97">
-        <v>2.153747625</v>
+        <v>2.1379476</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.58135137155702</v>
+        <v>1.958945971120222</v>
       </c>
       <c r="T97">
-        <v>9.391241035758076</v>
+        <v>11.7005626019281</v>
       </c>
       <c r="U97">
         <v>0.07190000000000001</v>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.528810122635548</v>
+        <v>2.502468350524762</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1301258388448087</v>
+        <v>0.1327926091117666</v>
       </c>
       <c r="C98">
-        <v>5.915342898597217</v>
+        <v>4.727723551884367</v>
       </c>
       <c r="D98">
-        <v>29.18334289859721</v>
+        <v>28.28872355188437</v>
       </c>
       <c r="E98">
-        <v>28.128</v>
+        <v>28.421</v>
       </c>
       <c r="F98">
-        <v>28.128</v>
+        <v>28.421</v>
       </c>
       <c r="G98">
         <v>4.86</v>
@@ -9451,45 +9451,45 @@
         <v>5.061</v>
       </c>
       <c r="M98">
-        <v>2.0224032</v>
+        <v>2.1543118</v>
       </c>
       <c r="N98">
-        <v>3.0385968</v>
+        <v>2.9066882</v>
       </c>
       <c r="O98">
-        <v>0.7596491999999999</v>
+        <v>0.7266720499999999</v>
       </c>
       <c r="P98">
-        <v>2.2789476</v>
+        <v>2.18001615</v>
       </c>
       <c r="Q98">
-        <v>2.1379476</v>
+        <v>2.03901615</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.958945971120217</v>
+        <v>2.588270303725551</v>
       </c>
       <c r="T98">
-        <v>11.70056260192807</v>
+        <v>15.54943187887809</v>
       </c>
       <c r="U98">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V98">
         <v>0.25</v>
       </c>
       <c r="W98">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y98">
-        <v>2.502468350524762</v>
+        <v>2.349242110635981</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1327926091117666</v>
+        <v>0.1326513793787245</v>
       </c>
       <c r="C99">
-        <v>4.727723551884367</v>
+        <v>4.480724074891761</v>
       </c>
       <c r="D99">
-        <v>28.28872355188437</v>
+        <v>28.33472407489176</v>
       </c>
       <c r="E99">
-        <v>28.421</v>
+        <v>28.714</v>
       </c>
       <c r="F99">
-        <v>28.421</v>
+        <v>28.714</v>
       </c>
       <c r="G99">
         <v>4.86</v>
@@ -9533,28 +9533,28 @@
         <v>5.061</v>
       </c>
       <c r="M99">
-        <v>2.1543118</v>
+        <v>2.1765212</v>
       </c>
       <c r="N99">
-        <v>2.9066882</v>
+        <v>2.8844788</v>
       </c>
       <c r="O99">
-        <v>0.7266720499999999</v>
+        <v>0.7211196999999999</v>
       </c>
       <c r="P99">
-        <v>2.18001615</v>
+        <v>2.1633591</v>
       </c>
       <c r="Q99">
-        <v>2.03901615</v>
+        <v>2.0223591</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.588270303725551</v>
+        <v>3.846918968936221</v>
       </c>
       <c r="T99">
-        <v>15.54943187887809</v>
+        <v>23.24717043277814</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.349242110635981</v>
+        <v>2.325270252364185</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1326513793787245</v>
+        <v>0.1325101496456823</v>
       </c>
       <c r="C100">
-        <v>4.480724074891761</v>
+        <v>4.233874445214862</v>
       </c>
       <c r="D100">
-        <v>28.33472407489176</v>
+        <v>28.38087444521486</v>
       </c>
       <c r="E100">
-        <v>28.714</v>
+        <v>29.007</v>
       </c>
       <c r="F100">
-        <v>28.714</v>
+        <v>29.007</v>
       </c>
       <c r="G100">
         <v>4.86</v>
@@ -9615,28 +9615,28 @@
         <v>5.061</v>
       </c>
       <c r="M100">
-        <v>2.1765212</v>
+        <v>2.1987306</v>
       </c>
       <c r="N100">
-        <v>2.8844788</v>
+        <v>2.8622694</v>
       </c>
       <c r="O100">
-        <v>0.7211196999999999</v>
+        <v>0.7155673499999999</v>
       </c>
       <c r="P100">
-        <v>2.1633591</v>
+        <v>2.14670205</v>
       </c>
       <c r="Q100">
-        <v>2.0223591</v>
+        <v>2.00570205</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.846918968936221</v>
+        <v>7.622864964568227</v>
       </c>
       <c r="T100">
-        <v>23.24717043277814</v>
+        <v>46.34038609447828</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.325270252364185</v>
+        <v>2.301782674057476</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1325101496456823</v>
-      </c>
-      <c r="C101">
-        <v>4.233874445214862</v>
-      </c>
-      <c r="D101">
-        <v>28.38087444521486</v>
-      </c>
-      <c r="E101">
-        <v>29.007</v>
-      </c>
-      <c r="F101">
-        <v>29.007</v>
-      </c>
-      <c r="G101">
-        <v>4.86</v>
-      </c>
-      <c r="H101">
-        <v>29.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.92</v>
-      </c>
-      <c r="K101">
-        <v>-0.141</v>
-      </c>
-      <c r="L101">
-        <v>5.061</v>
-      </c>
-      <c r="M101">
-        <v>2.1987306</v>
-      </c>
-      <c r="N101">
-        <v>2.8622694</v>
-      </c>
-      <c r="O101">
-        <v>0.7155673499999999</v>
-      </c>
-      <c r="P101">
-        <v>2.14670205</v>
-      </c>
-      <c r="Q101">
-        <v>2.00570205</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.622864964568227</v>
-      </c>
-      <c r="T101">
-        <v>46.34038609447828</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.05685</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.301782674057476</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
